--- a/docs/UAT-commission-plans.xlsx
+++ b/docs/UAT-commission-plans.xlsx
@@ -16,6 +16,7 @@
     <sheet name="5 Generation" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="6 Affiliate" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="7 ล็อกแผน" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="8 จ่ายเงิน" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="215">
   <si>
     <t xml:space="preserve">UAT — ตรวจการตั้งค่าและการแบ่งค่าคอมทั้ง 6 แผน</t>
   </si>
@@ -78,10 +79,16 @@
     <t xml:space="preserve">ราคาสินค้า ฿10,000.00 · PV ฿7,000.00 · อัตราผู้ขาย 10% · หัวหน้า 5/3/1% — เลือกให้คิดเลขในใจได้ ไม่ใช่ข้อเสนอว่าบริษัทจริงควรจ่ายเท่าไร (BR-7)</t>
   </si>
   <si>
+    <t xml:space="preserve">ตั้งจ่ายเงินได้เลย</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ตัวแทน UAT ทุกคนถูกกรอกบัญชีธนาคารและเอกสารยืนยันตัวตนไว้ให้แล้ว จึงขึ้นในคิว 'ตั้งจ่ายได้เลย' ได้ทันที — เลขบัญชีและเลขเอกสารขึ้นต้นด้วย UAT ทั้งหมด และเป็นหนังสือเดินทางไม่ใช่เลขบัตรประชาชน จึงไม่มีทางชนกับข้อมูลของคนจริง (ดูชีต 8)</t>
+  </si>
+  <si>
     <t xml:space="preserve">ยังไม่ครอบคลุม</t>
   </si>
   <si>
-    <t xml:space="preserve">ภาษีหัก ณ ที่จ่าย · การถอนเงิน · การคืนเงินและการกลับรายการ · ค่าคอมต่ออายุ · การแบ่งค่าคอมกับผู้ขายร่วม — แต่ละเรื่องมีทางเดินของตัวเองและควรมีชุดทดสอบแยก</t>
+    <t xml:space="preserve">การคืนเงินและการกลับรายการ · ค่าคอมต่ออายุ · การแบ่งค่าคอมกับผู้ขายร่วม — แต่ละเรื่องมีทางเดินของตัวเองและควรมีชุดทดสอบแยก</t>
   </si>
   <si>
     <t xml:space="preserve">สรุปผลรวมทุกแผน</t>
@@ -504,6 +511,12 @@
     <t xml:space="preserve">โหมด</t>
   </si>
   <si>
+    <t xml:space="preserve">ภาษีหัก ณ ที่จ่าย</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00%  ← บริษัทเดียวที่หัก ที่อื่นไม่หัก</t>
+  </si>
+  <si>
     <t xml:space="preserve">ผู้ขาย → ผู้แนะนำ</t>
   </si>
   <si>
@@ -522,6 +535,9 @@
     <t xml:space="preserve">· ลองสลับเป็นโหมด deductive: ผู้ขายต้องเหลือ ฿700 และยอดจ่ายออกรวมต้องเท่าเดิมที่ ฿1,000</t>
   </si>
   <si>
+    <t xml:space="preserve">· บริษัทนี้หักภาษี ณ ที่จ่าย 3% — ยอดในตารางนี้คือยอดก่อนหัก ดูยอดโอนจริงในชีต 8</t>
+  </si>
+  <si>
     <t xml:space="preserve">ล็อกแผนเมื่อบริษัทขายไปแล้ว</t>
   </si>
   <si>
@@ -595,6 +611,69 @@
   </si>
   <si>
     <t xml:space="preserve">· ช่องสีเหลืองคือช่องที่ผู้ทดสอบกรอก ช่องอื่นเป็นค่าที่คาดไว้ อย่าแก้</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ตั้งจ่าย → ตรวจสอบ → โอน</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ตัวแทน UAT ทุกคนมีบัญชีธนาคารและเอกสารยืนยันตัวตนครบแล้ว จึงขึ้นในคิว 'ตั้งจ่ายได้เลย' ได้ · เลขบัญชีและเลขเอกสารขึ้นต้นด้วย UAT และเป็นหนังสือเดินทางไม่ใช่เลขบัตรประชาชน จึงไม่มีทางชนกับข้อมูลของคนจริงในระบบค้นหา</t>
+  </si>
+  <si>
+    <t xml:space="preserve">แถบเหลือง 'มีค่าแนะนำ แต่ตั้งจ่ายไม่ได้' ต้องหายไป และทั้ง 4 คนย้ายมาอยู่ขั้นที่ 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UAT · Unilevel → จ่ายค่าแนะนำ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ขั้นที่ 1 ต้องขึ้น 4 คน รวม ฿1,900</t>
+  </si>
+  <si>
+    <t xml:space="preserve">หน้าเดียวกัน</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ติ๊กทั้ง 4 คนแล้วตั้งจ่าย → ต้องย้ายไปขั้นที่ 2 'รอคุณตรวจสอบ' ครบ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">อนุมัติ → ย้ายไปขั้นที่ 3 'รอฝ่ายบัญชีโอน' · ยอดยังเท่าเดิม</t>
+  </si>
+  <si>
+    <t xml:space="preserve">บันทึกการโอน → ย้ายไป 'โอนแล้ว' และแถวในบัญชีเปลี่ยนเป็นจ่ายแล้ว</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ขั้นที่ 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ไฟล์ CSV สำหรับโอน ดาวน์โหลดได้และมีเลขบัญชี UAT ครบทุกคน</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ปุ่มมุมขวาบน</t>
+  </si>
+  <si>
+    <t xml:space="preserve">บริษัท Affiliate หักภาษี ณ ที่จ่าย 3% — ยอดที่ได้ ฿1,000 ต้องโอนจริง ฿970 และหน้าจอต้องบอกทั้งสองยอด</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UAT · Affiliate → จ่ายค่าแนะนำ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">อีกห้าบริษัทต้องไม่มีบรรทัดภาษีเลย (ไม่ใช่ขึ้น 0.00)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">บริษัทอื่น ๆ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ลองลบบัญชีธนาคารของตัวแทนหนึ่งคนออก → เขาต้องหลุดจากขั้นที่ 1 กลับไปอยู่แถบเหลืองทันที</t>
+  </si>
+  <si>
+    <t xml:space="preserve">จัดการผู้ใช้ระบบ → กลับมาหน้าจ่าย</t>
+  </si>
+  <si>
+    <t xml:space="preserve">· อัตราภาษี 3% เป็นค่าทดสอบ ไม่ใช่ข้อเสนอว่าควรหักเท่าไร (BR-7) — อัตราจริงยังรอคุณกำหนด</t>
+  </si>
+  <si>
+    <t xml:space="preserve">· ข้อ 9 เป็นการทดสอบย้อนทาง: ด่านกันโอนเงินต้องปิดกลับได้ ไม่ใช่เปิดแล้วเปิดค้าง</t>
+  </si>
+  <si>
+    <t xml:space="preserve">· การคืนเงินและการกลับรายการค่าคอมยังไม่อยู่ในชุดนี้ — เป็นทางเดินอีกเส้นและควรมีชุดทดสอบแยก</t>
   </si>
 </sst>
 </file>
@@ -1114,7 +1193,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:C31"/>
+  <dimension ref="A2:C33"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -1188,7 +1267,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="3" t="s">
         <v>16</v>
       </c>
@@ -1196,36 +1275,26 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="5" t="s">
+    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6" t="s">
+      <c r="C21" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C23" s="6" t="s">
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="7" t="s">
+    <row r="25" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6"/>
+      <c r="B25" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="8" t="n">
-        <f aca="false">SUM('1 Unilevel'!D18:D21)</f>
-        <v>1900</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="7" t="s">
+      <c r="C25" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="C25" s="8" t="n">
-        <f aca="false">SUM('2 Binary'!D18:D20)</f>
-        <v>3000</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1233,8 +1302,8 @@
         <v>23</v>
       </c>
       <c r="C26" s="8" t="n">
-        <f aca="false">SUM('3 Matrix'!D18:D20)</f>
-        <v>1260</v>
+        <f aca="false">SUM('1 Unilevel'!D18:D21)</f>
+        <v>1900</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1242,8 +1311,8 @@
         <v>24</v>
       </c>
       <c r="C27" s="8" t="n">
-        <f aca="false">SUM('4 Stairstep'!D17:D19)</f>
-        <v>1500</v>
+        <f aca="false">SUM('2 Binary'!D18:D20)</f>
+        <v>3000</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1251,8 +1320,8 @@
         <v>25</v>
       </c>
       <c r="C28" s="8" t="n">
-        <f aca="false">SUM('5 Generation'!D17:D21)</f>
-        <v>1800</v>
+        <f aca="false">SUM('3 Matrix'!D18:D20)</f>
+        <v>1260</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1260,13 +1329,31 @@
         <v>26</v>
       </c>
       <c r="C29" s="8" t="n">
-        <f aca="false">SUM('6 Affiliate'!D16:D17)</f>
+        <f aca="false">SUM('4 Stairstep'!D17:D19)</f>
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="8" t="n">
+        <f aca="false">SUM('5 Generation'!D17:D21)</f>
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C31" s="8" t="n">
+        <f aca="false">SUM('6 Affiliate'!D17:D18)</f>
         <v>1300</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C31" s="2" t="s">
-        <v>27</v>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C33" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1298,33 +1385,33 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
@@ -1332,176 +1419,176 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C10" s="10"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C12" s="10"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C13" s="10"/>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C14" s="10"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D18" s="12" t="n">
         <v>1000</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F18" s="10"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D19" s="12" t="n">
         <v>500</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F19" s="10"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="B20" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="B20" s="11" t="s">
-        <v>61</v>
-      </c>
       <c r="C20" s="11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D20" s="12" t="n">
         <v>300</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F20" s="10"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D21" s="12" t="n">
         <v>100</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F21" s="10"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C22" s="13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D22" s="14" t="n">
         <f aca="false">SUM(D18:D21)</f>
@@ -1510,12 +1597,12 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
@@ -1525,7 +1612,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B26" s="15"/>
       <c r="C26" s="15"/>
@@ -1535,7 +1622,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1604,33 +1691,33 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
@@ -1638,158 +1725,158 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C10" s="10"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C12" s="10"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C13" s="10"/>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C14" s="10"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D18" s="12" t="n">
         <v>1000</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F18" s="10"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D19" s="12" t="n">
         <v>1000</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F19" s="10"/>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D20" s="12" t="n">
         <v>1000</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F20" s="10"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C21" s="13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D21" s="14" t="n">
         <f aca="false">SUM(D18:D20)</f>
@@ -1798,12 +1885,12 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B24" s="15"/>
       <c r="C24" s="15"/>
@@ -1813,7 +1900,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
@@ -1823,7 +1910,7 @@
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B26" s="15"/>
       <c r="C26" s="15"/>
@@ -1833,7 +1920,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B27" s="15"/>
       <c r="C27" s="15"/>
@@ -1843,7 +1930,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1914,33 +2001,33 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
@@ -1948,158 +2035,158 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C10" s="10"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C12" s="10"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C13" s="10"/>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C14" s="10"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D18" s="12" t="n">
         <v>700</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F18" s="10"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D19" s="12" t="n">
         <v>350</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F19" s="10"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="B20" s="11" t="s">
-        <v>106</v>
-      </c>
       <c r="C20" s="11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D20" s="12" t="n">
         <v>210</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F20" s="10"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C21" s="13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D21" s="14" t="n">
         <f aca="false">SUM(D18:D20)</f>
@@ -2108,12 +2195,12 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B24" s="15"/>
       <c r="C24" s="15"/>
@@ -2123,7 +2210,7 @@
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
@@ -2133,7 +2220,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B26" s="15"/>
       <c r="C26" s="15"/>
@@ -2143,7 +2230,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2213,33 +2300,33 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
@@ -2247,149 +2334,149 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C10" s="10"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C12" s="10"/>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C13" s="10"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D17" s="12" t="n">
         <v>500</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F17" s="10"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D18" s="12" t="n">
         <v>500</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F18" s="10"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="B19" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="B19" s="11" t="s">
-        <v>126</v>
-      </c>
       <c r="C19" s="11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D19" s="12" t="n">
         <v>500</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F19" s="10"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C20" s="13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D20" s="14" t="n">
         <f aca="false">SUM(D17:D19)</f>
@@ -2398,12 +2485,12 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
@@ -2413,7 +2500,7 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B24" s="15"/>
       <c r="C24" s="15"/>
@@ -2423,7 +2510,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
@@ -2433,7 +2520,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2503,33 +2590,33 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
@@ -2537,185 +2624,185 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C10" s="10"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C12" s="10"/>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C13" s="10"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D17" s="12" t="n">
         <v>1000</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F17" s="10"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="17" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D18" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F18" s="10"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D19" s="12" t="n">
         <v>500</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F19" s="10"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="17" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D20" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F20" s="10"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D21" s="12" t="n">
         <v>300</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F21" s="10"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C22" s="13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D22" s="14" t="n">
         <f aca="false">SUM(D17:D21)</f>
@@ -2724,12 +2811,12 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
@@ -2739,7 +2826,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B26" s="15"/>
       <c r="C26" s="15"/>
@@ -2749,7 +2836,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B27" s="15"/>
       <c r="C27" s="15"/>
@@ -2759,7 +2846,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2816,7 +2903,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
@@ -2829,33 +2916,33 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
@@ -2863,146 +2950,145 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C10" s="10"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C11" s="10"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>48</v>
+        <v>160</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C12" s="10"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="9" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B15" s="6" t="s">
+      <c r="B13" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="C13" s="10"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="6" t="s">
+    </row>
+    <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="B16" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="C16" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="D16" s="6" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="11" t="s">
+      <c r="E16" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="F16" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C16" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" s="12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="F16" s="10"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>160</v>
+        <v>59</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D17" s="12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="F17" s="10"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="12" t="n">
         <v>300</v>
       </c>
-      <c r="E17" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="F17" s="10"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="D18" s="14" t="n">
-        <f aca="false">SUM(D16:D17)</f>
+      <c r="E18" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="F18" s="10"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C19" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D19" s="14" t="n">
+        <f aca="false">SUM(D17:D18)</f>
         <v>1300</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="15" t="s">
-        <v>162</v>
-      </c>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B22" s="15"/>
       <c r="C22" s="15"/>
@@ -3010,26 +3096,30 @@
       <c r="E22" s="15"/>
       <c r="F22" s="15"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="16"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="B24" s="15"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="16"/>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
+      <c r="A26" s="5" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="16"/>
@@ -3047,11 +3137,28 @@
       <c r="E28" s="16"/>
       <c r="F28" s="16"/>
     </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="16"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="16"/>
+      <c r="B30" s="16"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+    </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A21:F21"/>
+  <mergeCells count="4">
     <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A25:F28"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A27:F30"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3079,26 +3186,26 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3106,10 +3213,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D5" s="10"/>
     </row>
@@ -3118,10 +3225,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="D6" s="10"/>
     </row>
@@ -3130,10 +3237,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="D7" s="10"/>
     </row>
@@ -3142,10 +3249,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="D8" s="10"/>
     </row>
@@ -3154,10 +3261,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="D9" s="10"/>
     </row>
@@ -3166,10 +3273,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="D10" s="10"/>
     </row>
@@ -3178,10 +3285,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="D11" s="10"/>
     </row>
@@ -3190,10 +3297,10 @@
         <v>8</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="D12" s="10"/>
     </row>
@@ -3202,21 +3309,21 @@
         <v>9</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="D13" s="10"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="19" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B17" s="19"/>
       <c r="C17" s="19"/>
@@ -3224,7 +3331,7 @@
     </row>
     <row r="18" customFormat="false" ht="12.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="19" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B18" s="19"/>
       <c r="C18" s="19"/>
@@ -3243,4 +3350,195 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D19"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="D5" s="10"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="D6" s="10"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="D7" s="10"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="D8" s="10"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="D9" s="10"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="D10" s="10"/>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="D11" s="10"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="D12" s="10"/>
+    </row>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="D13" s="10"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A19:D19"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>
--- a/docs/UAT-commission-plans.xlsx
+++ b/docs/UAT-commission-plans.xlsx
@@ -68,13 +68,13 @@
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
+      <i val="1"/>
+      <color rgb="00475569"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00475569"/>
+      <b val="1"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -210,14 +210,7 @@
     <xf numFmtId="4" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="4" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -225,6 +218,13 @@
     </xf>
     <xf numFmtId="4" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -592,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:C35"/>
+  <dimension ref="A2:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -700,130 +700,143 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
+    <row r="19" ht="75" customHeight="1">
       <c r="B19" s="3" t="inlineStr">
         <is>
+          <t>ทำไมตัวเลขถึงไม่กลม ๆ เท่ากัน</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>ชุดนี้ออกแบบให้ “ผิดแล้วต้องเห็น” — ทุกแถวในแผนเดียวกันได้ไม่เท่ากัน และทุกแผนมีคนหนึ่งคนที่ ต้องได้ ฿0 เพราะกติกาสั่งให้หยุด ไม่ใช่เพราะสายงานหมดคนพอดี
+ชุดก่อนหน้านี้ตั้งสองขาของ Binary ให้เท่ากัน และตั้งส่วนต่างของ Stairstep ให้เท่ากันทั้งสามแถว ซึ่งแปลว่าต่อให้เครื่องคิดผิด ตัวเลขบนหน้าจอก็ยังเหมือนเดิม</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
           <t>ค่าที่ใช้ทดสอบ</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>ราคาสินค้า ฿10,000.00 · PV ฿7,000.00 · อัตราผู้ขาย 10% · หัวหน้า 5/3/1% — เลือกให้คิดเลขในใจได้ ไม่ใช่ข้อเสนอว่าบริษัทจริงควรจ่ายเท่าไร (BR-7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="45" customHeight="1">
-      <c r="B21" s="3" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>ราคาสินค้า ฿10,000.00 · PV ฿7,000.00 · อัตราผู้ขาย 10% · หัวหน้า Unilevel 5/3/1% · ขั้น Stairstep 5/12/20/25% — เลือกให้คิดเลขในใจได้ ไม่ใช่ข้อเสนอว่าบริษัทจริงควรจ่ายเท่าไร (BR-7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="45" customHeight="1">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>ตั้งจ่ายเงินได้เลย</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>ตัวแทน UAT ทุกคนถูกกรอกบัญชีธนาคารและเอกสารยืนยันตัวตนไว้ให้แล้ว จึงขึ้นในคิว 'ตั้งจ่ายได้เลย' ได้ทันที — เลขบัญชีและเลขเอกสารขึ้นต้นด้วย UAT ทั้งหมด และเป็นหนังสือเดินทางไม่ใช่เลขบัตรประชาชน จึงไม่มีทางชนกับข้อมูลของคนจริง (ดูชีต 8)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="B23" s="3" t="inlineStr">
+    <row r="25" ht="30" customHeight="1">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>ยังไม่ครอบคลุม</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>การคืนเงินและการกลับรายการ · ค่าคอมต่ออายุ · การแบ่งค่าคอมกับผู้ขายร่วม — แต่ละเรื่องมีทางเดินของตัวเองและควรมีชุดทดสอบแยก</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>สรุปผลรวมทุกแผน</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="6" t="inlineStr"/>
-      <c r="B27" s="6" t="inlineStr">
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="6" t="inlineStr"/>
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>แผน</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>ยอดจ่ายออกรวมที่ควรได้ (บาท)</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="7" t="inlineStr">
+    <row r="30">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>Unilevel</t>
         </is>
       </c>
-      <c r="C28" s="8">
-        <f>SUM('1 Unilevel'!D32:D35)</f>
+      <c r="C30" s="8">
+        <f>SUM('1 Unilevel'!D32:D36)</f>
         <v/>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="7" t="inlineStr">
+    <row r="31">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>Binary</t>
         </is>
       </c>
-      <c r="C29" s="8">
+      <c r="C31" s="8">
         <f>SUM('2 Binary'!D34:D36)</f>
         <v/>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>Matrix</t>
-        </is>
-      </c>
-      <c r="C30" s="8">
-        <f>SUM('3 Matrix'!D37:D39)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>Stairstep</t>
-        </is>
-      </c>
-      <c r="C31" s="8">
-        <f>SUM('4 Stairstep'!D34:D36)</f>
-        <v/>
-      </c>
-    </row>
     <row r="32">
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Generation</t>
+          <t>Matrix</t>
         </is>
       </c>
       <c r="C32" s="8">
-        <f>SUM('5 Generation'!D32:D36)</f>
+        <f>SUM('3 Matrix'!D38:D41)</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="7" t="inlineStr">
         <is>
+          <t>Stairstep</t>
+        </is>
+      </c>
+      <c r="C33" s="8">
+        <f>SUM('4 Stairstep'!D35:D38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Generation</t>
+        </is>
+      </c>
+      <c r="C34" s="8">
+        <f>SUM('5 Generation'!D33:D38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="7" t="inlineStr">
+        <is>
           <t>พันธมิตร (Affiliate)</t>
         </is>
       </c>
-      <c r="C33" s="8">
-        <f>SUM('6 Affiliate'!D28:D29)</f>
+      <c r="C35" s="8">
+        <f>SUM('6 Affiliate'!D28:D30)</f>
         <v/>
       </c>
     </row>
-    <row r="35">
-      <c r="C35" s="2" t="inlineStr">
+    <row r="37">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>ยอดของ Binary รวมส่วนที่ต้องรันรอบจับคู่ก่อนถึงจะเกิดขึ้น · ยอดของ Matrix คิดจาก PV ไม่ใช่ราคา</t>
         </is>
@@ -840,7 +853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1262,7 +1275,7 @@
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>ผู้ขาย → หัวหน้าชั้น 1 → หัวหน้าชั้น 2 → หัวหน้าชั้น 3</t>
+          <t>ผู้ขาย → ชั้น 1 → ชั้น 2 → ชั้น 3 → ชั้น 4 (ชั้น 4 ไม่มีอัตรา จึงต้องไม่ได้เงิน)</t>
         </is>
       </c>
       <c r="C28" s="9" t="n"/>
@@ -1418,52 +1431,86 @@
       <c r="F35" s="13" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="C36" s="15" t="inlineStr">
+      <c r="A36" s="15" t="inlineStr">
+        <is>
+          <t>UAT หัวหน้าชั้น 4</t>
+        </is>
+      </c>
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D36" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="16" t="inlineStr">
+        <is>
+          <t>ไม่ได้ตั้งอัตราชั้นที่ 4 ไว้ → ต้องไม่มีแถวในบัญชีเลย ไม่ใช่แถว ฿0</t>
+        </is>
+      </c>
+      <c r="F36" s="13" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="C37" s="18" t="inlineStr">
         <is>
           <t>รวมจ่ายออก</t>
         </is>
       </c>
-      <c r="D36" s="16">
-        <f>SUM(D32:D35)</f>
+      <c r="D37" s="19">
+        <f>SUM(D32:D36)</f>
         <v/>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>ขั้นที่ 3 — จุดที่มักพลาด</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>· ผู้ขายต้องได้เต็ม ฿1,000 — ถ้าน้อยกว่านี้ แปลว่าระบบไปหักค่าหัวหน้าจากผู้ขาย ซึ่งผิดโหมด additive</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>· ผู้ขายต้องได้เต็ม ฿1,000 — ถ้าน้อยกว่านี้ แปลว่าระบบไปหักค่าหัวหน้าจากผู้ขาย ซึ่งผิดโหมด additive</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
           <t>· ต้องมีครบ 4 แถว — ขาดแถวไหนแปลว่าหัวหน้าคนนั้นถูกข้าม (มักเพราะยังไม่ผ่าน Basic ตาม BR-1)</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>· ชั้น 4 มีตัวตนจริงและผ่าน Basic แล้ว แต่ต้องไม่มีแถวในบัญชีเลย เพราะไม่ได้ตั้งอัตราชั้นที่ 4 ไว้ — ถ้าเห็นแถว ฿0 หรือเห็นเขาได้อัตราของชั้นอื่น นั่นคือบั๊ก</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>บันทึกของผู้ทดสอบ</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="17" t="n"/>
-    </row>
-    <row r="44"/>
-    <row r="45"/>
+    <row r="45">
+      <c r="A45" s="20" t="n"/>
+    </row>
     <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="26">
+    <mergeCell ref="A41:F41"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="A27:F27"/>
@@ -1471,8 +1518,8 @@
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A43:F46"/>
     <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A42:F42"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="B9:D9"/>
@@ -1480,12 +1527,12 @@
     <mergeCell ref="B24:D24"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A45:F48"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="A40:F40"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B25:D25"/>
-    <mergeCell ref="A39:F39"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="B18:D18"/>
@@ -1495,694 +1542,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F49"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Binary — จ่ายจากขาที่น้อยกว่า และจ่ายเป็นรอบ</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>บริษัท: uat-plan-binary · ฐานการคำนวณ: ราคาขาย ฿10,000.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>กติกา: ผู้ขายแต่ละคนได้อัตราของตัวเองทันทีที่ปิดการขาย ส่วนผู้สนับสนุนจะได้เมื่อ รอบจับคู่ทำงาน โดยคิดจากยอดขาที่น้อยกว่า</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>ขั้นที่ 1 — เปิดหน้า “ค่าแนะนำ” ของบริษัทนี้ แล้วไล่ตรวจทีละช่อง</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>แถบสีคือหัวข้อของส่วนบนหน้าจอ · ชื่อในคอลัมน์ “ช่องบนหน้าจอ” เขียนตรงตามที่หน้าจอเขียนไว้</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>ช่องบนหน้าจอ</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>ต้องเป็น</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="10" t="n"/>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>หมายเหตุ</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>ตรงไหม</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>ขั้นที่ 2 · แถวชิปเลือกแผน</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="n"/>
-      <c r="C8" s="9" t="n"/>
-      <c r="D8" s="9" t="n"/>
-      <c r="E8" s="9" t="n"/>
-      <c r="F8" s="10" t="n"/>
-    </row>
-    <row r="9" ht="14" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>แผนที่เลือกอยู่</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>Binary</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="10" t="n"/>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>ชิปของแผนอื่นต้องกดไม่ได้และมีรูปกุญแจ</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>ขั้นที่ 2 · การ์ด “ค่าแนะนำคิดจากอะไร”</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="n"/>
-      <c r="C10" s="9" t="n"/>
-      <c r="D10" s="9" t="n"/>
-      <c r="E10" s="9" t="n"/>
-      <c r="F10" s="10" t="n"/>
-    </row>
-    <row r="11" ht="14" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>ฐานการคำนวณ</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>ราคาขาย</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="10" t="n"/>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>ทั้งสองปุ่มกดไม่ได้</t>
-        </is>
-      </c>
-      <c r="F11" s="13" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>ขั้นที่ 2 · ฟอร์ม “ค่าตั้งระดับบริษัทของแผน Binary”</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="n"/>
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="9" t="n"/>
-      <c r="E12" s="9" t="n"/>
-      <c r="F12" s="10" t="n"/>
-    </row>
-    <row r="13" ht="14" customHeight="1">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>รูปแบบอัตรา Matched</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>% ของยอด Matched</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="n"/>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>อีกตัวเลือกคือ “จำนวนคงที่ (บาท)”</t>
-        </is>
-      </c>
-      <c r="F13" s="13" t="inlineStr"/>
-    </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>อัตรา (%)</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="10" t="n"/>
-      <c r="E14" s="12" t="inlineStr">
-        <is>
-          <t>ชื่อช่องเปลี่ยนเป็น “จำนวน (บาท)” ถ้าสลับรูปแบบข้างบน</t>
-        </is>
-      </c>
-      <c r="F14" s="13" t="inlineStr"/>
-    </row>
-    <row r="15" ht="14" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>รอบคำนวณ</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>รายสัปดาห์</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="10" t="n"/>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>อีกสองตัวเลือกคือ ทุก 2 สัปดาห์ / รายเดือน</t>
-        </is>
-      </c>
-      <c r="F15" s="13" t="inlineStr"/>
-    </row>
-    <row r="16" ht="14" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>เพดานจ่าย/รอบ (บาท, ว่าง = ไม่จำกัด)</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="inlineStr">
-        <is>
-          <t>เว้นว่าง</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="10" t="n"/>
-      <c r="E16" s="12" t="inlineStr"/>
-      <c r="F16" s="13" t="inlineStr"/>
-    </row>
-    <row r="17" ht="14" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>ยกยอดที่ไม่ Matched ไปรอบถัดไป</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>ติ๊กไว้</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="n"/>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="12" t="inlineStr">
-        <is>
-          <t>ช่องติ๊ก ไม่ใช่ช่องกรอก</t>
-        </is>
-      </c>
-      <c r="F17" s="13" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="inlineStr">
-        <is>
-          <t>ขั้นที่ 2 · “ประวัติรอบ Matching (อ่านอย่างเดียว)”</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="n"/>
-      <c r="C18" s="9" t="n"/>
-      <c r="D18" s="9" t="n"/>
-      <c r="E18" s="9" t="n"/>
-      <c r="F18" s="10" t="n"/>
-    </row>
-    <row r="19" ht="14" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>ก่อนรันคำสั่งรอบจับคู่</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>“ยังไม่มีรอบ Matching”</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="10" t="n"/>
-      <c r="E19" s="12" t="inlineStr">
-        <is>
-          <t>ว่างตรงนี้ถูกต้อง</t>
-        </is>
-      </c>
-      <c r="F19" s="13" t="inlineStr"/>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>หลังรันคำสั่งรอบจับคู่</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="inlineStr">
-        <is>
-          <t>1 แถว · ซ้าย ฿10,000.00 · ขวา ฿10,000.00 · Matched ฿10,000.00 · ยกยอด ฿0.00 · ป้าย “จ่ายแล้ว”</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="n"/>
-      <c r="D20" s="10" t="n"/>
-      <c r="E20" s="12" t="inlineStr">
-        <is>
-          <t>ถ้าป้ายยังเป็น “ไม่มีค่าแนะนำ” แปลว่ารอบทำงานแล้วแต่ไม่ได้ลงบัญชี — เป็นสิ่งที่ต้องรายงาน</t>
-        </is>
-      </c>
-      <c r="F20" s="13" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>ขั้นที่ 3 · สมาชิกผู้ขายได้กี่เปอร์เซ็นต์</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="9" t="n"/>
-      <c r="D21" s="9" t="n"/>
-      <c r="E21" s="9" t="n"/>
-      <c r="F21" s="10" t="n"/>
-    </row>
-    <row r="22" ht="14" customHeight="1">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>ค่าเริ่มต้นทั้งบริษัท</t>
-        </is>
-      </c>
-      <c r="B22" s="12" t="inlineStr">
-        <is>
-          <t>10.00%</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="10" t="n"/>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>ผู้ขายแต่ละขาได้จากตรงนี้ ไม่ใช่จากอัตรา Matched</t>
-        </is>
-      </c>
-      <c r="F22" s="13" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>ขั้นที่ 4 · ส่วนเพิ่มเติม</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="9" t="n"/>
-      <c r="D23" s="9" t="n"/>
-      <c r="E23" s="9" t="n"/>
-      <c r="F23" s="10" t="n"/>
-    </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>4.1 เงินของหัวหน้าทีมมาจากไหน</t>
-        </is>
-      </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>บริษัทจ่ายเพิ่ม</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="n"/>
-      <c r="D24" s="10" t="n"/>
-      <c r="E24" s="12" t="inlineStr">
-        <is>
-          <t>ป้าย “ตอนนี้: บริษัทจ่ายเพิ่ม” ที่หัวการ์ด · เป็นค่าเริ่มต้นของระบบ คำสั่ง seed ไม่ได้แตะ</t>
-        </is>
-      </c>
-      <c r="F24" s="13" t="inlineStr"/>
-    </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>4.2 จ่ายขึ้นไปกี่ชั้น</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>กล่องนี้ต้องไม่ขึ้นเลย</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="n"/>
-      <c r="D25" s="10" t="n"/>
-      <c r="E25" s="12" t="inlineStr">
-        <is>
-          <t>มีเฉพาะบริษัทที่ใช้แผน Unilevel — แผนอื่นจำกัดชั้นด้วยค่าของตัวเอง</t>
-        </is>
-      </c>
-      <c r="F25" s="13" t="inlineStr"/>
-    </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>4.3 อัตราหัวหน้าทีม · ค่าเริ่มต้นทั้งบริษัท</t>
-        </is>
-      </c>
-      <c r="B26" s="12" t="inlineStr">
-        <is>
-          <t>ไม่มีรายการ</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="n"/>
-      <c r="D26" s="10" t="n"/>
-      <c r="E26" s="12" t="inlineStr">
-        <is>
-          <t>แผนนี้จ่ายชั้นบนผ่านรอบจับคู่ ไม่ได้ใช้อัตราหัวหน้าทีม — ว่างตรงนี้ถูกต้อง</t>
-        </is>
-      </c>
-      <c r="F26" s="13" t="inlineStr"/>
-    </row>
-    <row r="27" ht="14" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>4.7 ยอดขั้นต่ำในการเบิก</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>เว้นว่าง</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="n"/>
-      <c r="D27" s="10" t="n"/>
-      <c r="E27" s="12" t="inlineStr">
-        <is>
-          <t>เว้นว่าง = ไม่มีขั้นต่ำ</t>
-        </is>
-      </c>
-      <c r="F27" s="13" t="inlineStr"/>
-    </row>
-    <row r="28" ht="14" customHeight="1">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>4.8 ภาษีหัก ณ ที่จ่าย</t>
-        </is>
-      </c>
-      <c r="B28" s="12" t="inlineStr">
-        <is>
-          <t>ไม่หัก (เว้นว่าง)</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="n"/>
-      <c r="D28" s="10" t="n"/>
-      <c r="E28" s="12" t="inlineStr">
-        <is>
-          <t>มีบริษัทเดียวในชุดนี้ที่หัก คือ Affiliate</t>
-        </is>
-      </c>
-      <c r="F28" s="13" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>ไม่ได้อยู่บนหน้านี้ — ตรวจที่อื่น</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="n"/>
-      <c r="C29" s="9" t="n"/>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="9" t="n"/>
-      <c r="F29" s="10" t="n"/>
-    </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>ขาซ้าย / ขาขวา ของแต่ละคน</t>
-        </is>
-      </c>
-      <c r="B30" s="12" t="inlineStr">
-        <is>
-          <t>ขาซ้าย 1 คน · ขาขวา 1 คน ใต้ผู้สนับสนุน</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="n"/>
-      <c r="D30" s="10" t="n"/>
-      <c r="E30" s="12" t="inlineStr">
-        <is>
-          <t>ตั้งที่เมนูจัดการผู้ใช้ระบบ — ตัวแทนที่ไม่ได้ตั้งขาจะไม่ส่งยอดขึ้นไปเลยและไม่มีคำเตือน</t>
-        </is>
-      </c>
-      <c r="F30" s="13" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>ขั้นที่ 2 — ตรวจว่าค่าคอมที่ลงบัญชีตรงกับนี้</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>ใคร</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>ได้จาก (earned_via)</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>อัตรา</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>ควรได้ (บาท)</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>ที่มาของตัวเลข</t>
-        </is>
-      </c>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t>ผ่าน / ไม่ผ่าน</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="12" t="inlineStr">
-        <is>
-          <t>UAT ขาซ้าย</t>
-        </is>
-      </c>
-      <c r="B34" s="12" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
-      <c r="C34" s="12" t="inlineStr">
-        <is>
-          <t>10.00%</t>
-        </is>
-      </c>
-      <c r="D34" s="14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E34" s="12" t="inlineStr">
-        <is>
-          <t>10% ของ ฿10,000</t>
-        </is>
-      </c>
-      <c r="F34" s="13" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="12" t="inlineStr">
-        <is>
-          <t>UAT ขาขวา</t>
-        </is>
-      </c>
-      <c r="B35" s="12" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
-      <c r="C35" s="12" t="inlineStr">
-        <is>
-          <t>10.00%</t>
-        </is>
-      </c>
-      <c r="D35" s="14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E35" s="12" t="inlineStr">
-        <is>
-          <t>10% ของ ฿10,000</t>
-        </is>
-      </c>
-      <c r="F35" s="13" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="12" t="inlineStr">
-        <is>
-          <t>UAT ผู้สนับสนุน</t>
-        </is>
-      </c>
-      <c r="B36" s="12" t="inlineStr">
-        <is>
-          <t>binary_match</t>
-        </is>
-      </c>
-      <c r="C36" s="12" t="inlineStr">
-        <is>
-          <t>10.00%</t>
-        </is>
-      </c>
-      <c r="D36" s="14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E36" s="12" t="inlineStr">
-        <is>
-          <t>หลังรันรอบจับคู่เท่านั้น: จับคู่ได้ min(฿10,000, ฿10,000) = ฿10,000 → 10%</t>
-        </is>
-      </c>
-      <c r="F36" s="13" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="C37" s="15" t="inlineStr">
-        <is>
-          <t>รวมจ่ายออก</t>
-        </is>
-      </c>
-      <c r="D37" s="16">
-        <f>SUM(D34:D36)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>ขั้นที่ 3 — จุดที่มักพลาด</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>· ก่อนรันรอบจับคู่ ผู้สนับสนุนต้องได้ ฿0 — อันนี้ถูกต้อง ไม่ใช่บั๊ก Binary ไม่จ่ายต่อการขาย</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>· สั่งรันรอบ: php artisan commissions:run-binary-cycles</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>· ระวัง: คำสั่งนั้นประมวลผลทุกบริษัทที่ตั้ง Binary ไว้ ไม่ใช่เฉพาะ UAT — ตัวคำสั่ง seed จะบอกท้ายผลลัพธ์ว่ามีบริษัทอื่นติดร่างแหไหม</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="15" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>· ตัวแทนที่ไม่ได้ตั้งขา (ซ้าย/ขวา) จะไม่ส่งยอดขึ้นไปเลย และไม่มีข้อความเตือนใด ๆ</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>บันทึกของผู้ทดสอบ</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="17" t="n"/>
-    </row>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-  </sheetData>
-  <mergeCells count="29">
-    <mergeCell ref="A41:F41"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A42:F42"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="A43:F43"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="A46:F49"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2202,21 +1561,21 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Matrix — ผังกว้างจำกัด และคิดจาก PV</t>
+          <t>Binary — จ่ายจากขาที่น้อยกว่า และจ่ายเป็นรอบ</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>บริษัท: uat-plan-matrix · ฐานการคำนวณ: PV ฿7,000.00  (ไม่ใช่ราคาขาย ฿10,000.00)</t>
+          <t>บริษัท: uat-plan-binary · ฐานการคำนวณ: ราคาขาย ฿10,000.00</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>กติกา: จ่ายขึ้นไปตามผัง matrix ของตัวเอง (คนละต้นกับสายหัวหน้า) ตามอัตราของแต่ละชั้น บริษัทนี้ตั้งใจให้คิดจาก PV เพื่อทดสอบฐานการคำนวณ</t>
+          <t>กติกา: ผู้ขายแต่ละคนได้อัตราของตัวเองทันทีที่ปิดการขาย ส่วนผู้สนับสนุนจะได้เมื่อ รอบจับคู่ทำงาน โดยคิดจากยอดขาที่น้อยกว่า</t>
         </is>
       </c>
     </row>
@@ -2278,7 +1637,7 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Matrix</t>
+          <t>Binary</t>
         </is>
       </c>
       <c r="C9" s="9" t="n"/>
@@ -2302,7 +1661,7 @@
       <c r="E10" s="9" t="n"/>
       <c r="F10" s="10" t="n"/>
     </row>
-    <row r="11" ht="28" customHeight="1">
+    <row r="11" ht="14" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
           <t>ฐานการคำนวณ</t>
@@ -2310,14 +1669,14 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>PV  ← บริษัทเดียวในชุดนี้ที่ใช้ PV</t>
+          <t>ราคาขาย</t>
         </is>
       </c>
       <c r="C11" s="9" t="n"/>
       <c r="D11" s="10" t="n"/>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>ปุ่ม “PV” ต้องมีเครื่องหมายถูก และขั้นที่ 3 ต้องมีแถบฟ้าเตือนว่าคิดจาก PV ไม่ใช่ราคาขาย</t>
+          <t>ทั้งสองปุ่มกดไม่ได้</t>
         </is>
       </c>
       <c r="F11" s="13" t="inlineStr"/>
@@ -2325,7 +1684,7 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>ขั้นที่ 2 · ตาราง “PV ของแต่ละสินค้า”</t>
+          <t>ขั้นที่ 2 · ฟอร์ม “ค่าตั้งระดับบริษัทของแผน Binary”</t>
         </is>
       </c>
       <c r="B12" s="9" t="n"/>
@@ -2334,22 +1693,22 @@
       <c r="E12" s="9" t="n"/>
       <c r="F12" s="10" t="n"/>
     </row>
-    <row r="13" ht="28" customHeight="1">
+    <row r="13" ht="14" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>UAT Package</t>
+          <t>รูปแบบอัตรา Matched</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>7,000.00</t>
+          <t>% ของยอด Matched</t>
         </is>
       </c>
       <c r="C13" s="9" t="n"/>
       <c r="D13" s="10" t="n"/>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>บรรทัดบนต้องบอก “ราคาขาย ฿10,000.00” — สองตัวเลขนี้ต้องไม่เท่ากัน ไม่งั้นทดสอบฐาน PV ไม่ได้</t>
+          <t>อีกตัวเลือกคือ “จำนวนคงที่ (บาท)”</t>
         </is>
       </c>
       <c r="F13" s="13" t="inlineStr"/>
@@ -2357,44 +1716,52 @@
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>ป้าย “ยังไม่ได้กำหนด n รายการ”</t>
+          <t>อัตรา (%)</t>
         </is>
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>ต้องไม่ขึ้น</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C14" s="9" t="n"/>
       <c r="D14" s="10" t="n"/>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>ขึ้นเมื่อมีสินค้าที่ยังไม่ได้ใส่ PV — ตารางนี้จะโผล่เฉพาะบริษัทที่ใช้ฐาน PV</t>
+          <t>ชื่อช่องเปลี่ยนเป็น “จำนวน (บาท)” ถ้าสลับรูปแบบข้างบน</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr"/>
     </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>ขั้นที่ 2 · ฟอร์ม “ค่าตั้งระดับบริษัทของแผน Matrix”</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="n"/>
+    <row r="15" ht="14" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>รอบคำนวณ</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>รายสัปดาห์</t>
+        </is>
+      </c>
       <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="9" t="n"/>
-      <c r="F15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>อีกสองตัวเลือกคือ ทุก 2 สัปดาห์ / รายเดือน</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr"/>
     </row>
     <row r="16" ht="14" customHeight="1">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>ความกว้าง (Width)</t>
+          <t>เพดานจ่าย/รอบ (บาท, ว่าง = ไม่จำกัด)</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>เว้นว่าง</t>
         </is>
       </c>
       <c r="C16" s="9" t="n"/>
@@ -2405,67 +1772,71 @@
     <row r="17" ht="14" customHeight="1">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>ความลึก (Depth)</t>
+          <t>ยกยอดที่ไม่ Matched ไปรอบถัดไป</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>ติ๊กไว้</t>
         </is>
       </c>
       <c r="C17" s="9" t="n"/>
       <c r="D17" s="10" t="n"/>
-      <c r="E17" s="12" t="inlineStr"/>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>ช่องติ๊ก ไม่ใช่ช่องกรอก</t>
+        </is>
+      </c>
       <c r="F17" s="13" t="inlineStr"/>
     </row>
-    <row r="18" ht="14" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>กฎ Spillover</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>Breadth-first (กว้างก่อน)</t>
-        </is>
-      </c>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>ขั้นที่ 2 · “ประวัติรอบ Matching (อ่านอย่างเดียว)”</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="n"/>
       <c r="C18" s="9" t="n"/>
-      <c r="D18" s="10" t="n"/>
-      <c r="E18" s="12" t="inlineStr">
-        <is>
-          <t>ตอนนี้มีตัวเลือกเดียว</t>
-        </is>
-      </c>
-      <c r="F18" s="13" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>ขั้นที่ 2 · กล่อง “ตัวอย่างโครงสร้าง”</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="9" t="n"/>
+      <c r="F18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="14" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>ก่อนรันคำสั่งรอบจับคู่</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>“ยังไม่มีรอบ Matching”</t>
+        </is>
+      </c>
       <c r="C19" s="9" t="n"/>
-      <c r="D19" s="9" t="n"/>
-      <c r="E19" s="9" t="n"/>
-      <c r="F19" s="10" t="n"/>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>ว่างตรงนี้ถูกต้อง</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr"/>
     </row>
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>หัวข้อกล่อง</t>
+          <t>หลังรันคำสั่งรอบจับคู่</t>
         </is>
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>ตัวอย่างโครงสร้าง 3 x 2</t>
+          <t>1 แถว · ซ้าย ฿10,000.00 · ขวา ฿10,000.00 · Matched ฿10,000.00 · ยกยอด ฿0.00 · ป้าย “จ่ายแล้ว”</t>
         </is>
       </c>
       <c r="C20" s="9" t="n"/>
       <c r="D20" s="10" t="n"/>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>ต้องวาด 2 แถว แถวละ 3 ช่อง ป้ายกำกับ 1.1–1.3 และ 2.1–2.3</t>
+          <t>ถ้าป้ายยังเป็น “ไม่มีค่าแนะนำ” แปลว่ารอบทำงานแล้วแต่ไม่ได้ลงบัญชี — เป็นสิ่งที่ต้องรายงาน</t>
         </is>
       </c>
       <c r="F20" s="13" t="inlineStr"/>
@@ -2473,7 +1844,7 @@
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>ขั้นที่ 2 · รายการ “อัตราค่าแนะนำตาม Level”</t>
+          <t>ขั้นที่ 3 · สมาชิกผู้ขายได้กี่เปอร์เซ็นต์</t>
         </is>
       </c>
       <c r="B21" s="9" t="n"/>
@@ -2485,368 +1856,341 @@
     <row r="22" ht="14" customHeight="1">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>Level 1</t>
+          <t>ค่าเริ่มต้นทั้งบริษัท</t>
         </is>
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>Level 1 — 5.00%</t>
+          <t>10.00%</t>
         </is>
       </c>
       <c r="C22" s="9" t="n"/>
       <c r="D22" s="10" t="n"/>
-      <c r="E22" s="12" t="inlineStr"/>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>ผู้ขายแต่ละขาได้จากตรงนี้ ไม่ใช่จากอัตรา Matched</t>
+        </is>
+      </c>
       <c r="F22" s="13" t="inlineStr"/>
     </row>
-    <row r="23" ht="14" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>Level 2</t>
-        </is>
-      </c>
-      <c r="B23" s="12" t="inlineStr">
-        <is>
-          <t>Level 2 — 3.00%</t>
-        </is>
-      </c>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>ขั้นที่ 4 · ส่วนเพิ่มเติม</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="n"/>
       <c r="C23" s="9" t="n"/>
-      <c r="D23" s="10" t="n"/>
-      <c r="E23" s="12" t="inlineStr">
-        <is>
-          <t>ต้องมีแค่ 2 รายการ ให้เท่ากับความลึกที่ตั้งไว้</t>
-        </is>
-      </c>
-      <c r="F23" s="13" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>ขั้นที่ 3 · สมาชิกผู้ขายได้กี่เปอร์เซ็นต์</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="n"/>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>4.1 เงินของหัวหน้าทีมมาจากไหน</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>บริษัทจ่ายเพิ่ม</t>
+        </is>
+      </c>
       <c r="C24" s="9" t="n"/>
-      <c r="D24" s="9" t="n"/>
-      <c r="E24" s="9" t="n"/>
-      <c r="F24" s="10" t="n"/>
+      <c r="D24" s="10" t="n"/>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>ป้าย “ตอนนี้: บริษัทจ่ายเพิ่ม” ที่หัวการ์ด · เป็นค่าเริ่มต้นของระบบ คำสั่ง seed ไม่ได้แตะ</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="inlineStr"/>
     </row>
     <row r="25" ht="28" customHeight="1">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>ค่าเริ่มต้นทั้งบริษัท</t>
+          <t>4.2 จ่ายขึ้นไปกี่ชั้น</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>10.00%</t>
+          <t>กล่องนี้ต้องไม่ขึ้นเลย</t>
         </is>
       </c>
       <c r="C25" s="9" t="n"/>
       <c r="D25" s="10" t="n"/>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>10% ของ PV ฿7,000 = ฿700 ไม่ใช่ ฿1,000 — ขั้นที่ 3 ต้องมีแถบฟ้าบอกเรื่องนี้ไว้</t>
+          <t>มีเฉพาะบริษัทที่ใช้แผน Unilevel — แผนอื่นจำกัดชั้นด้วยค่าของตัวเอง</t>
         </is>
       </c>
       <c r="F25" s="13" t="inlineStr"/>
     </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>ขั้นที่ 4 · ส่วนเพิ่มเติม</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="n"/>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>4.3 อัตราหัวหน้าทีม · ค่าเริ่มต้นทั้งบริษัท</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>ไม่มีรายการ</t>
+        </is>
+      </c>
       <c r="C26" s="9" t="n"/>
-      <c r="D26" s="9" t="n"/>
-      <c r="E26" s="9" t="n"/>
-      <c r="F26" s="10" t="n"/>
-    </row>
-    <row r="27" ht="28" customHeight="1">
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>แผนนี้จ่ายชั้นบนผ่านรอบจับคู่ ไม่ได้ใช้อัตราหัวหน้าทีม — ว่างตรงนี้ถูกต้อง</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="inlineStr"/>
+    </row>
+    <row r="27" ht="14" customHeight="1">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>4.1 เงินของหัวหน้าทีมมาจากไหน</t>
+          <t>4.7 ยอดขั้นต่ำในการเบิก</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>บริษัทจ่ายเพิ่ม</t>
+          <t>เว้นว่าง</t>
         </is>
       </c>
       <c r="C27" s="9" t="n"/>
       <c r="D27" s="10" t="n"/>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>ป้าย “ตอนนี้: บริษัทจ่ายเพิ่ม” ที่หัวการ์ด · เป็นค่าเริ่มต้นของระบบ คำสั่ง seed ไม่ได้แตะ</t>
+          <t>เว้นว่าง = ไม่มีขั้นต่ำ</t>
         </is>
       </c>
       <c r="F27" s="13" t="inlineStr"/>
     </row>
-    <row r="28" ht="28" customHeight="1">
+    <row r="28" ht="14" customHeight="1">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>4.2 จ่ายขึ้นไปกี่ชั้น</t>
+          <t>4.8 ภาษีหัก ณ ที่จ่าย</t>
         </is>
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>กล่องนี้ต้องไม่ขึ้นเลย</t>
+          <t>ไม่หัก (เว้นว่าง)</t>
         </is>
       </c>
       <c r="C28" s="9" t="n"/>
       <c r="D28" s="10" t="n"/>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>มีเฉพาะบริษัทที่ใช้แผน Unilevel — แผนอื่นจำกัดชั้นด้วยค่าของตัวเอง</t>
+          <t>มีบริษัทเดียวในชุดนี้ที่หัก คือ Affiliate</t>
         </is>
       </c>
       <c r="F28" s="13" t="inlineStr"/>
     </row>
-    <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>4.3 อัตราหัวหน้าทีม · ค่าเริ่มต้นทั้งบริษัท</t>
-        </is>
-      </c>
-      <c r="B29" s="12" t="inlineStr">
-        <is>
-          <t>ไม่มีรายการ</t>
-        </is>
-      </c>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>ไม่ได้อยู่บนหน้านี้ — ตรวจที่อื่น</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="n"/>
       <c r="C29" s="9" t="n"/>
-      <c r="D29" s="10" t="n"/>
-      <c r="E29" s="12" t="inlineStr">
-        <is>
-          <t>แผนนี้จ่ายชั้นบนด้วยอัตราตาม Level ข้างบน ไม่ได้ใช้อัตราหัวหน้าทีม</t>
-        </is>
-      </c>
-      <c r="F29" s="13" t="inlineStr"/>
-    </row>
-    <row r="30" ht="14" customHeight="1">
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="28" customHeight="1">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>4.7 ยอดขั้นต่ำในการเบิก</t>
+          <t>ขาซ้าย / ขาขวา ของแต่ละคน</t>
         </is>
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>เว้นว่าง</t>
+          <t>ขาซ้าย 1 คน (ขาย 2 ดีล) · ขาขวา 1 คน (ขาย 1 ดีล) ใต้ผู้สนับสนุน — ตั้งใจให้สองขาไม่เท่ากัน</t>
         </is>
       </c>
       <c r="C30" s="9" t="n"/>
       <c r="D30" s="10" t="n"/>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>เว้นว่าง = ไม่มีขั้นต่ำ</t>
+          <t>ตั้งที่เมนูจัดการผู้ใช้ระบบ — ตัวแทนที่ไม่ได้ตั้งขาจะไม่ส่งยอดขึ้นไปเลยและไม่มีคำเตือน</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr"/>
     </row>
-    <row r="31" ht="14" customHeight="1">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>4.8 ภาษีหัก ณ ที่จ่าย</t>
-        </is>
-      </c>
-      <c r="B31" s="12" t="inlineStr">
-        <is>
-          <t>ไม่หัก (เว้นว่าง)</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="n"/>
-      <c r="D31" s="10" t="n"/>
-      <c r="E31" s="12" t="inlineStr">
-        <is>
-          <t>มีบริษัทเดียวในชุดนี้ที่หัก คือ Affiliate</t>
-        </is>
-      </c>
-      <c r="F31" s="13" t="inlineStr"/>
-    </row>
     <row r="32">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>ไม่ได้อยู่บนหน้านี้ — ตรวจที่อื่น</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="n"/>
-      <c r="C32" s="9" t="n"/>
-      <c r="D32" s="9" t="n"/>
-      <c r="E32" s="9" t="n"/>
-      <c r="F32" s="10" t="n"/>
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>ขั้นที่ 2 — ตรวจว่าค่าคอมที่ลงบัญชีตรงกับนี้</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="12" t="inlineStr">
-        <is>
-          <t>ผังวางตำแหน่ง (matrix placements)</t>
-        </is>
-      </c>
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t>ชั้นบนสุด → ชั้นกลาง → ผู้ขาย</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="n"/>
-      <c r="D33" s="10" t="n"/>
-      <c r="E33" s="12" t="inlineStr">
-        <is>
-          <t>ไม่มีหน้าจอตั้งค่า — คำสั่ง seed วางให้ตรงกับสายหัวหน้า ในระบบจริงสองอย่างนี้ต่างกันได้</t>
-        </is>
-      </c>
-      <c r="F33" s="13" t="inlineStr"/>
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>ใคร</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>ได้จาก (earned_via)</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>อัตรา</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>ควรได้ (บาท)</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>ที่มาของตัวเลข</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>ผ่าน / ไม่ผ่าน</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>UAT ขาซ้าย</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>10.00%</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>ขาย 2 ดีล ได้ดีลละ ฿1,000 (2 แถวในบัญชี)</t>
+        </is>
+      </c>
+      <c r="F34" s="13" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>ขั้นที่ 2 — ตรวจว่าค่าคอมที่ลงบัญชีตรงกับนี้</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>ใคร</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>ได้จาก (earned_via)</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>อัตรา</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>ควรได้ (บาท)</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>ที่มาของตัวเลข</t>
-        </is>
-      </c>
-      <c r="F36" s="6" t="inlineStr">
-        <is>
-          <t>ผ่าน / ไม่ผ่าน</t>
-        </is>
-      </c>
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>UAT ขาขวา</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>10.00%</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>ขาย 1 ดีล</t>
+        </is>
+      </c>
+      <c r="F35" s="13" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>UAT ผู้สนับสนุน</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>binary_match</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>10.00%</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E36" s="12" t="inlineStr">
+        <is>
+          <t>หลังรันรอบจับคู่เท่านั้น: จับคู่ได้ min(ซ้าย ฿20,000, ขวา ฿10,000) = ฿10,000 → 10% · ถ้าได้ ฿2,000 แปลว่าระบบคิดจากขาที่มากกว่า ซึ่งผิด</t>
+        </is>
+      </c>
+      <c r="F36" s="13" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="12" t="inlineStr">
-        <is>
-          <t>UAT ผู้ขาย</t>
-        </is>
-      </c>
-      <c r="B37" s="12" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
-      <c r="C37" s="12" t="inlineStr">
-        <is>
-          <t>10.00%</t>
-        </is>
-      </c>
-      <c r="D37" s="14" t="n">
-        <v>700</v>
-      </c>
-      <c r="E37" s="12" t="inlineStr">
-        <is>
-          <t>10% ของ PV ฿7,000 ไม่ใช่ของราคา ฿10,000</t>
-        </is>
-      </c>
-      <c r="F37" s="13" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="12" t="inlineStr">
-        <is>
-          <t>UAT ชั้นกลาง</t>
-        </is>
-      </c>
-      <c r="B38" s="12" t="inlineStr">
-        <is>
-          <t>matrix_override</t>
-        </is>
-      </c>
-      <c r="C38" s="12" t="inlineStr">
-        <is>
-          <t>5.00%</t>
-        </is>
-      </c>
-      <c r="D38" s="14" t="n">
-        <v>350</v>
-      </c>
-      <c r="E38" s="12" t="inlineStr">
-        <is>
-          <t>5% ของ PV ฿7,000</t>
-        </is>
-      </c>
-      <c r="F38" s="13" t="inlineStr"/>
+      <c r="C37" s="18" t="inlineStr">
+        <is>
+          <t>รวมจ่ายออก</t>
+        </is>
+      </c>
+      <c r="D37" s="19">
+        <f>SUM(D34:D36)</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="12" t="inlineStr">
-        <is>
-          <t>UAT ชั้นบนสุด</t>
-        </is>
-      </c>
-      <c r="B39" s="12" t="inlineStr">
-        <is>
-          <t>matrix_override</t>
-        </is>
-      </c>
-      <c r="C39" s="12" t="inlineStr">
-        <is>
-          <t>3.00%</t>
-        </is>
-      </c>
-      <c r="D39" s="14" t="n">
-        <v>210</v>
-      </c>
-      <c r="E39" s="12" t="inlineStr">
-        <is>
-          <t>3% ของ PV ฿7,000</t>
-        </is>
-      </c>
-      <c r="F39" s="13" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="C40" s="15" t="inlineStr">
-        <is>
-          <t>รวมจ่ายออก</t>
-        </is>
-      </c>
-      <c r="D40" s="16">
-        <f>SUM(D37:D39)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>ขั้นที่ 3 — จุดที่มักพลาด</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>· ก่อนรันรอบจับคู่ ผู้สนับสนุนต้องได้ ฿0 — อันนี้ถูกต้อง ไม่ใช่บั๊ก Binary ไม่จ่ายต่อการขาย</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>· สั่งรันรอบ: php artisan commissions:run-binary-cycles</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>· ระวัง: คำสั่งนั้นประมวลผลทุกบริษัทที่ตั้ง Binary ไว้ ไม่ใช่เฉพาะ UAT — ตัวคำสั่ง seed จะบอกท้ายผลลัพธ์ว่ามีบริษัทอื่นติดร่างแหไหม</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>· ตัวเลขทั้งหมดต้องเป็น 70% ของบริษัทที่คิดจากราคา — ถ้าได้ ฿1,000 แทน ฿700 แปลว่าฐาน PV ไม่ถูกใช้</t>
+          <t>· ตัวแทนที่ไม่ได้ตั้งขา (ซ้าย/ขวา) จะไม่ส่งยอดขึ้นไปเลย และไม่มีข้อความเตือนใด ๆ</t>
         </is>
       </c>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>· Matrix เดินตามผังของตัวเอง ไม่ใช่สายหัวหน้า — ตัวแทนที่มีหัวหน้าแต่ไม่ถูกวางในผัง จะไม่ได้อะไรเลยโดยไม่มีคำเตือน</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="15" customHeight="1">
+          <t>· สองขาตั้งใจให้ไม่เท่ากัน (ซ้าย ฿20,000 · ขวา ฿10,000) — ถ้าเท่ากัน min() กับ max() จะให้คำตอบเดียวกัน แล้วชุดทดสอบจะพิสูจน์กติกาของแผนนี้ไม่ได้เลย</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="30" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>· ลองลดราคาสินค้าแล้วขายใหม่: ค่าคอมต้องไม่ลดตาม เพราะคิดจาก PV</t>
+          <t>· หลังรันรอบ ให้ดูหน้า “ประวัติรอบ Matching”: ต้องขึ้น ซ้าย ฿20,000 · ขวา ฿10,000 · Matched ฿10,000 · ยกยอด ฿10,000 — ช่องยกยอดคือที่เดียวที่บอกได้ว่าการยกยอดทำงานจริง</t>
         </is>
       </c>
     </row>
@@ -2858,56 +2202,56 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="17" t="n"/>
+      <c r="A48" s="20" t="n"/>
     </row>
     <row r="49"/>
     <row r="50"/>
     <row r="51"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A41:F41"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B23:D23"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A18:F18"/>
     <mergeCell ref="A21:F21"/>
-    <mergeCell ref="B29:D29"/>
     <mergeCell ref="B28:D28"/>
-    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A23:F23"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="A48:F51"/>
     <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A29:F29"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="A43:F43"/>
-    <mergeCell ref="B33:D33"/>
     <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A19:F19"/>
     <mergeCell ref="A44:F44"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="A40:F40"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B25:D25"/>
-    <mergeCell ref="A15:F15"/>
     <mergeCell ref="B16:D16"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="B31:D31"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A45:F45"/>
-    <mergeCell ref="B18:D18"/>
     <mergeCell ref="B27:D27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2921,21 +2265,21 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Stairstep — หัวหน้าได้เฉพาะส่วนต่างของขั้น</t>
+          <t>Matrix — ผังกว้างจำกัด และคิดจาก PV</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>บริษัท: uat-plan-stairstep-breakaway · ฐานการคำนวณ: ราคาขาย ฿10,000.00</t>
+          <t>บริษัท: uat-plan-matrix · ฐานการคำนวณ: PV ฿7,000.00  (ไม่ใช่ราคาขาย ฿10,000.00)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>กติกา: หัวหน้าแต่ละคนได้เฉพาะส่วนที่อัตราขั้นของตัวเองสูงกว่าขั้นของลูกทีม และหยุดทันทีที่เจอคนที่ถึงขั้นตัดสาย</t>
+          <t>กติกา: จ่ายขึ้นไปตามผัง matrix ของตัวเอง (คนละต้นกับสายหัวหน้า) ตามอัตราของแต่ละชั้น บริษัทนี้ตั้งใจให้คิดจาก PV เพื่อทดสอบฐานการคำนวณ</t>
         </is>
       </c>
     </row>
@@ -2997,14 +2341,14 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>อันดับ (Stairstep)</t>
+          <t>Matrix</t>
         </is>
       </c>
       <c r="C9" s="9" t="n"/>
       <c r="D9" s="10" t="n"/>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>ชื่อบนชิปเขียนแบบนี้ ไม่ใช่ “Stairstep” เฉย ๆ</t>
+          <t>ชิปของแผนอื่นต้องกดไม่ได้และมีรูปกุญแจ</t>
         </is>
       </c>
       <c r="F9" s="13" t="inlineStr"/>
@@ -3021,7 +2365,7 @@
       <c r="E10" s="9" t="n"/>
       <c r="F10" s="10" t="n"/>
     </row>
-    <row r="11" ht="14" customHeight="1">
+    <row r="11" ht="28" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
           <t>ฐานการคำนวณ</t>
@@ -3029,14 +2373,14 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>ราคาขาย</t>
+          <t>PV  ← บริษัทเดียวในชุดนี้ที่ใช้ PV</t>
         </is>
       </c>
       <c r="C11" s="9" t="n"/>
       <c r="D11" s="10" t="n"/>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>ทั้งสองปุ่มกดไม่ได้</t>
+          <t>ปุ่ม “PV” ต้องมีเครื่องหมายถูก และขั้นที่ 3 ต้องมีแถบฟ้าเตือนว่าคิดจาก PV ไม่ใช่ราคาขาย</t>
         </is>
       </c>
       <c r="F11" s="13" t="inlineStr"/>
@@ -3044,7 +2388,7 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>ขั้นที่ 2 · ฟอร์ม “ค่าตั้งระดับบริษัทของแผนอันดับ (Stairstep)”</t>
+          <t>ขั้นที่ 2 · ตาราง “PV ของแต่ละสินค้า”</t>
         </is>
       </c>
       <c r="B12" s="9" t="n"/>
@@ -3056,554 +2400,632 @@
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>หน้าต่างคำนวณยอดย้อนหลัง (วัน)</t>
+          <t>UAT Package</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>7,000.00</t>
         </is>
       </c>
       <c r="C13" s="9" t="n"/>
       <c r="D13" s="10" t="n"/>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>ช่องนี้เคยว่างเพราะคำสั่ง seed ไม่ได้เขียนแถวค่าตั้งให้ — แก้แล้ว 2026-09-22</t>
+          <t>บรรทัดบนต้องบอก “ราคาขาย ฿10,000.00” — สองตัวเลขนี้ต้องไม่เท่ากัน ไม่งั้นทดสอบฐาน PV ไม่ได้</t>
         </is>
       </c>
       <c r="F13" s="13" t="inlineStr"/>
     </row>
-    <row r="14" ht="14" customHeight="1">
+    <row r="14" ht="28" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>ความถี่คำนวณอันดับใหม่</t>
+          <t>ป้าย “ยังไม่ได้กำหนด n รายการ”</t>
         </is>
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>รายเดือน</t>
+          <t>ต้องไม่ขึ้น</t>
         </is>
       </c>
       <c r="C14" s="9" t="n"/>
       <c r="D14" s="10" t="n"/>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>อีกสองตัวเลือกคือ รายวัน / รายสัปดาห์</t>
+          <t>ขึ้นเมื่อมีสินค้าที่ยังไม่ได้ใส่ PV — ตารางนี้จะโผล่เฉพาะบริษัทที่ใช้ฐาน PV</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr"/>
     </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>นับยอดของใคร</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>เฉพาะยอดที่ขายเอง (ค่าเริ่มต้น — เท่าเดิม)</t>
-        </is>
-      </c>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>ขั้นที่ 2 · ฟอร์ม “ค่าตั้งระดับบริษัทของแผน Matrix”</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n"/>
       <c r="C15" s="9" t="n"/>
-      <c r="D15" s="10" t="n"/>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>ตั้งเป็นค่าเริ่มต้นของระบบไว้ · ถ้าเลือก “ยอดทั้งทีม” ต้องมีข้อความเหลืองเตือนขึ้นทันที</t>
-        </is>
-      </c>
-      <c r="F15" s="13" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>ขั้นที่ 2 · รายการ “บันไดอันดับ”</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="10" t="n"/>
+    </row>
+    <row r="16" ht="14" customHeight="1">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>ความกว้าง (Width)</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="9" t="n"/>
-      <c r="F16" s="10" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="12" t="inlineStr"/>
+      <c r="F16" s="13" t="inlineStr"/>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>อันดับที่ 1</t>
+          <t>ความลึก (Depth)</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>1. UAT ขั้นเริ่มต้น · ยอดขั้นต่ำ 0.00 · อัตรา 5.00%</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C17" s="9" t="n"/>
       <c r="D17" s="10" t="n"/>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>ชื่อขั้นขึ้นต้นด้วย “UAT ” ทุกอัน — ถ้าไม่มีคำนี้ แปลว่าเป็นข้อมูลของบริษัทอื่น</t>
+          <t>ตั้งใจให้น้อยกว่าจำนวนอัตราที่ตั้งไว้ข้างล่าง เพื่อให้ตรวจได้ว่าความลึกนี้บังคับจริง</t>
         </is>
       </c>
       <c r="F17" s="13" t="inlineStr"/>
     </row>
-    <row r="18" ht="28" customHeight="1">
+    <row r="18" ht="14" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>อันดับที่ 2</t>
+          <t>กฎ Spillover</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>2. UAT ขั้นผู้นำ · ยอดขั้นต่ำ 50,000.00 · อัตรา 10.00%</t>
+          <t>Breadth-first (กว้างก่อน)</t>
         </is>
       </c>
       <c r="C18" s="9" t="n"/>
       <c r="D18" s="10" t="n"/>
-      <c r="E18" s="12" t="inlineStr"/>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>ตอนนี้มีตัวเลือกเดียว</t>
+        </is>
+      </c>
       <c r="F18" s="13" t="inlineStr"/>
     </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>อันดับที่ 3</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>3. UAT ขั้นผู้จัดการ (Breakaway) · ยอดขั้นต่ำ 200,000.00 · อัตรา 15.00%</t>
-        </is>
-      </c>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>ขั้นที่ 2 · กล่อง “ตัวอย่างโครงสร้าง”</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="n"/>
       <c r="C19" s="9" t="n"/>
-      <c r="D19" s="10" t="n"/>
-      <c r="E19" s="12" t="inlineStr">
-        <is>
-          <t>ป้าย “(Breakaway)” สีเหลืองต้องขึ้นเฉพาะอันดับนี้</t>
-        </is>
-      </c>
-      <c r="F19" s="13" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>ขั้นที่ 3 · สมาชิกผู้ขายได้กี่เปอร์เซ็นต์</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="n"/>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="9" t="n"/>
+      <c r="F19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>หัวข้อกล่อง</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>ตัวอย่างโครงสร้าง 3 x 2</t>
+        </is>
+      </c>
       <c r="C20" s="9" t="n"/>
-      <c r="D20" s="9" t="n"/>
-      <c r="E20" s="9" t="n"/>
-      <c r="F20" s="10" t="n"/>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>ค่าเริ่มต้นทั้งบริษัท</t>
-        </is>
-      </c>
-      <c r="B21" s="12" t="inlineStr">
-        <is>
-          <t>5.00%</t>
-        </is>
-      </c>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>ต้องวาด 2 แถว แถวละ 3 ช่อง ป้ายกำกับ 1.1–1.3 และ 2.1–2.3</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>ขั้นที่ 2 · รายการ “อัตราค่าแนะนำตาม Level”</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="n"/>
       <c r="C21" s="9" t="n"/>
-      <c r="D21" s="10" t="n"/>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>ตั้งให้เท่ากับอัตราของ “UAT ขั้นเริ่มต้น” โดยตั้งใจ — อ่านหมายเหตุในขั้นที่ 3 ของชีตนี้</t>
-        </is>
-      </c>
-      <c r="F21" s="13" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>ขั้นที่ 4 · ส่วนเพิ่มเติม</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="n"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="10" t="n"/>
+    </row>
+    <row r="22" ht="14" customHeight="1">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>Level 1</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>Level 1 — 5.00%</t>
+        </is>
+      </c>
       <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="10" t="n"/>
-    </row>
-    <row r="23" ht="28" customHeight="1">
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="12" t="inlineStr"/>
+      <c r="F22" s="13" t="inlineStr"/>
+    </row>
+    <row r="23" ht="14" customHeight="1">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>4.1 เงินของหัวหน้าทีมมาจากไหน</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>บริษัทจ่ายเพิ่ม</t>
+          <t>Level 2 — 3.00%</t>
         </is>
       </c>
       <c r="C23" s="9" t="n"/>
       <c r="D23" s="10" t="n"/>
-      <c r="E23" s="12" t="inlineStr">
-        <is>
-          <t>ป้าย “ตอนนี้: บริษัทจ่ายเพิ่ม” ที่หัวการ์ด · เป็นค่าเริ่มต้นของระบบ คำสั่ง seed ไม่ได้แตะ</t>
-        </is>
-      </c>
+      <c r="E23" s="12" t="inlineStr"/>
       <c r="F23" s="13" t="inlineStr"/>
     </row>
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>4.2 จ่ายขึ้นไปกี่ชั้น</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>กล่องนี้ต้องไม่ขึ้นเลย</t>
+          <t>Level 3 — 1.00%</t>
         </is>
       </c>
       <c r="C24" s="9" t="n"/>
       <c r="D24" s="10" t="n"/>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>มีเฉพาะบริษัทที่ใช้แผน Unilevel — แผนอื่นจำกัดชั้นด้วยค่าของตัวเอง</t>
+          <t>ตั้งไว้แต่ไม่มีวันได้จ่าย เพราะผังลึกแค่ 2 ชั้น — เป็นตัวล่อให้จับได้ว่าความลึกบังคับจริงหรือเปล่า</t>
         </is>
       </c>
       <c r="F24" s="13" t="inlineStr"/>
     </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>4.3 อัตราหัวหน้าทีม · ค่าเริ่มต้นทั้งบริษัท</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>ไม่มีรายการ</t>
-        </is>
-      </c>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>ขั้นที่ 3 · สมาชิกผู้ขายได้กี่เปอร์เซ็นต์</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="n"/>
       <c r="C25" s="9" t="n"/>
-      <c r="D25" s="10" t="n"/>
-      <c r="E25" s="12" t="inlineStr">
-        <is>
-          <t>แผนนี้จ่ายชั้นบนด้วยส่วนต่างของอันดับ ไม่ได้ใช้อัตราหัวหน้าทีม</t>
-        </is>
-      </c>
-      <c r="F25" s="13" t="inlineStr"/>
-    </row>
-    <row r="26" ht="14" customHeight="1">
+      <c r="D25" s="9" t="n"/>
+      <c r="E25" s="9" t="n"/>
+      <c r="F25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="28" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>4.7 ยอดขั้นต่ำในการเบิก</t>
+          <t>ค่าเริ่มต้นทั้งบริษัท</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>เว้นว่าง</t>
+          <t>10.00%</t>
         </is>
       </c>
       <c r="C26" s="9" t="n"/>
       <c r="D26" s="10" t="n"/>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>เว้นว่าง = ไม่มีขั้นต่ำ</t>
+          <t>10% ของ PV ฿7,000 = ฿700 ไม่ใช่ ฿1,000 — ขั้นที่ 3 ต้องมีแถบฟ้าบอกเรื่องนี้ไว้</t>
         </is>
       </c>
       <c r="F26" s="13" t="inlineStr"/>
     </row>
-    <row r="27" ht="14" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>4.8 ภาษีหัก ณ ที่จ่าย</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>ไม่หัก (เว้นว่าง)</t>
-        </is>
-      </c>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>ขั้นที่ 4 · ส่วนเพิ่มเติม</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="n"/>
       <c r="C27" s="9" t="n"/>
-      <c r="D27" s="10" t="n"/>
-      <c r="E27" s="12" t="inlineStr">
-        <is>
-          <t>มีบริษัทเดียวในชุดนี้ที่หัก คือ Affiliate</t>
-        </is>
-      </c>
-      <c r="F27" s="13" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="11" t="inlineStr">
-        <is>
-          <t>ไม่ได้อยู่บนหน้านี้ — ตรวจที่อื่น</t>
-        </is>
-      </c>
-      <c r="B28" s="9" t="n"/>
+      <c r="D27" s="9" t="n"/>
+      <c r="E27" s="9" t="n"/>
+      <c r="F27" s="10" t="n"/>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>4.1 เงินของหัวหน้าทีมมาจากไหน</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>บริษัทจ่ายเพิ่ม</t>
+        </is>
+      </c>
       <c r="C28" s="9" t="n"/>
-      <c r="D28" s="9" t="n"/>
-      <c r="E28" s="9" t="n"/>
-      <c r="F28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>ป้าย “ตอนนี้: บริษัทจ่ายเพิ่ม” ที่หัวการ์ด · เป็นค่าเริ่มต้นของระบบ คำสั่ง seed ไม่ได้แตะ</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="inlineStr"/>
     </row>
     <row r="29" ht="28" customHeight="1">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>อันดับปัจจุบันของแต่ละคน</t>
+          <t>4.2 จ่ายขึ้นไปกี่ชั้น</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>ผู้ขาย = ขั้นเริ่มต้น · ผู้นำ = ขั้นผู้นำ · ผู้จัดการ = ขั้นผู้จัดการ</t>
+          <t>กล่องนี้ต้องไม่ขึ้นเลย</t>
         </is>
       </c>
       <c r="C29" s="9" t="n"/>
       <c r="D29" s="10" t="n"/>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>คำสั่ง seed วางอันดับให้โดยตรง ไม่ได้รอรอบคำนวณ — หน้าค่าแนะนำไม่มีช่องให้ดูหรือแก้อันดับรายคน</t>
+          <t>มีเฉพาะบริษัทที่ใช้แผน Unilevel — แผนอื่นจำกัดชั้นด้วยค่าของตัวเอง</t>
         </is>
       </c>
       <c r="F29" s="13" t="inlineStr"/>
     </row>
-    <row r="30" ht="14" customHeight="1">
+    <row r="30" ht="28" customHeight="1">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>สายงาน (ใครเป็นหัวหน้าของใคร)</t>
+          <t>4.3 อัตราหัวหน้าทีม · ค่าเริ่มต้นทั้งบริษัท</t>
         </is>
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>ผู้ขาย → ผู้นำ → ผู้จัดการ (ตัดสาย)</t>
+          <t>ไม่มีรายการ</t>
         </is>
       </c>
       <c r="C30" s="9" t="n"/>
       <c r="D30" s="10" t="n"/>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>ดูที่เมนูจัดการผู้ใช้ระบบ ช่อง “หัวหน้า”</t>
+          <t>แผนนี้จ่ายชั้นบนด้วยอัตราตาม Level ข้างบน ไม่ได้ใช้อัตราหัวหน้าทีม</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr"/>
     </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+    <row r="31" ht="14" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>4.7 ยอดขั้นต่ำในการเบิก</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>เว้นว่าง</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>เว้นว่าง = ไม่มีขั้นต่ำ</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="inlineStr"/>
+    </row>
+    <row r="32" ht="14" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>4.8 ภาษีหัก ณ ที่จ่าย</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>ไม่หัก (เว้นว่าง)</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>มีบริษัทเดียวในชุดนี้ที่หัก คือ Affiliate</t>
+        </is>
+      </c>
+      <c r="F32" s="13" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>ไม่ได้อยู่บนหน้านี้ — ตรวจที่อื่น</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="n"/>
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>ผังวางตำแหน่ง (matrix placements)</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>ชั้นบนสุด → ชั้นกลาง → ผู้ขาย</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>ไม่มีหน้าจอตั้งค่า — คำสั่ง seed วางให้ตรงกับสายหัวหน้า ในระบบจริงสองอย่างนี้ต่างกันได้</t>
+        </is>
+      </c>
+      <c r="F34" s="13" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>ขั้นที่ 2 — ตรวจว่าค่าคอมที่ลงบัญชีตรงกับนี้</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>ใคร</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>ได้จาก (earned_via)</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>อัตรา</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>ควรได้ (บาท)</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="E37" s="6" t="inlineStr">
         <is>
           <t>ที่มาของตัวเลข</t>
         </is>
       </c>
-      <c r="F33" s="6" t="inlineStr">
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <t>ผ่าน / ไม่ผ่าน</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="12" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
         <is>
           <t>UAT ผู้ขาย</t>
         </is>
       </c>
-      <c r="B34" s="12" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>direct</t>
         </is>
       </c>
-      <c r="C34" s="12" t="inlineStr">
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>10.00%</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="n">
+        <v>700</v>
+      </c>
+      <c r="E38" s="12" t="inlineStr">
+        <is>
+          <t>10% ของ PV ฿7,000 ไม่ใช่ของราคา ฿10,000</t>
+        </is>
+      </c>
+      <c r="F38" s="13" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>UAT ชั้นกลาง</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>matrix_override</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr">
         <is>
           <t>5.00%</t>
         </is>
       </c>
-      <c r="D34" s="14" t="n">
-        <v>500</v>
-      </c>
-      <c r="E34" s="12" t="inlineStr">
-        <is>
-          <t>5% ของ ฿10,000</t>
-        </is>
-      </c>
-      <c r="F34" s="13" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="12" t="inlineStr">
-        <is>
-          <t>UAT ผู้นำ</t>
-        </is>
-      </c>
-      <c r="B35" s="12" t="inlineStr">
-        <is>
-          <t>stairstep_override</t>
-        </is>
-      </c>
-      <c r="C35" s="12" t="inlineStr">
-        <is>
-          <t>5.00%</t>
-        </is>
-      </c>
-      <c r="D35" s="14" t="n">
-        <v>500</v>
-      </c>
-      <c r="E35" s="12" t="inlineStr">
-        <is>
-          <t>ส่วนต่าง 10% − 5% = 5%</t>
-        </is>
-      </c>
-      <c r="F35" s="13" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="12" t="inlineStr">
-        <is>
-          <t>UAT ผู้จัดการ (ตัดสาย)</t>
-        </is>
-      </c>
-      <c r="B36" s="12" t="inlineStr">
-        <is>
-          <t>stairstep_override</t>
-        </is>
-      </c>
-      <c r="C36" s="12" t="inlineStr">
-        <is>
-          <t>5.00%</t>
-        </is>
-      </c>
-      <c r="D36" s="14" t="n">
-        <v>500</v>
-      </c>
-      <c r="E36" s="12" t="inlineStr">
-        <is>
-          <t>ส่วนต่าง 15% − 10% = 5%</t>
-        </is>
-      </c>
-      <c r="F36" s="13" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="C37" s="15" t="inlineStr">
+      <c r="D39" s="14" t="n">
+        <v>350</v>
+      </c>
+      <c r="E39" s="12" t="inlineStr">
+        <is>
+          <t>5% ของ PV ฿7,000</t>
+        </is>
+      </c>
+      <c r="F39" s="13" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>UAT ชั้นบนสุด</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>matrix_override</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>3.00%</t>
+        </is>
+      </c>
+      <c r="D40" s="14" t="n">
+        <v>210</v>
+      </c>
+      <c r="E40" s="12" t="inlineStr">
+        <is>
+          <t>3% ของ PV ฿7,000</t>
+        </is>
+      </c>
+      <c r="F40" s="13" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="15" t="inlineStr">
+        <is>
+          <t>UAT ชั้นเหนือสุด</t>
+        </is>
+      </c>
+      <c r="B41" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C41" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D41" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="16" t="inlineStr">
+        <is>
+          <t>อยู่ชั้นที่ 3 ของผัง · ตั้งอัตราชั้น 3 ไว้ 1% แต่ผังลึกแค่ 2 ชั้น → ต้องไม่มีแถว ถ้าได้ ฿70 แปลว่าระบบไม่สนความลึกที่ตั้งไว้</t>
+        </is>
+      </c>
+      <c r="F41" s="13" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="C42" s="18" t="inlineStr">
         <is>
           <t>รวมจ่ายออก</t>
         </is>
       </c>
-      <c r="D37" s="16">
-        <f>SUM(D34:D36)</f>
+      <c r="D42" s="19">
+        <f>SUM(D38:D41)</f>
         <v/>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>ขั้นที่ 3 — จุดที่มักพลาด</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>· สามแถวได้เท่ากันโดยบังเอิญจากค่าที่ตั้งไว้ — ตรวจที่ชื่อคน อย่าตรวจแค่ยอด</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>· คำถามออกแบบที่ยังค้าง: อัตราของผู้ขายมาจาก commission_rules ไม่ได้มาจากขั้นของตัวเอง ชุดทดสอบนี้จงใจตั้งให้ตรงกันไว้ ถ้าตั้งไม่ตรงกันจะมี 'อัตราผู้ขาย' สองค่าบนหน้าจอเดียว</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>· ลองเลื่อนผู้ขายขึ้นเป็นขั้นตัดสาย: หัวหน้าทุกคนเหนือขึ้นไปต้องได้ ฿0 ทันที</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>· ฟอร์มสามช่องบนสุด (หน้าต่างย้อนหลัง / ความถี่ / นับยอดของใคร) เคยว่างเปล่าจนถึง 2026-09-22 เพราะคำสั่ง seed ไม่ได้เขียนแถวค่าตั้งให้ — ถ้ายังว่างอยู่ แปลว่ารันคำสั่ง seed เวอร์ชันเก่า</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>· ค่าในสามช่องนั้นใช้โดยรอบคำนวณอันดับอัตโนมัติ ซึ่งชุดทดสอบนี้ไม่ได้รัน (อันดับของทุกคนถูกวางไว้โดยตรง) — จึงเปลี่ยนค่าแล้วยอดในขั้นที่ 2 ต้องไม่ขยับ</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>· ตัวเลขทั้งหมดต้องเป็น 70% ของบริษัทที่คิดจากราคา — ถ้าได้ ฿1,000 แทน ฿700 แปลว่าฐาน PV ไม่ถูกใช้</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>· Matrix เดินตามผังของตัวเอง ไม่ใช่สายหัวหน้า — ตัวแทนที่มีหัวหน้าแต่ไม่ถูกวางในผัง จะไม่ได้อะไรเลยโดยไม่มีคำเตือน</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>· ลองลดราคาสินค้าแล้วขายใหม่: ค่าคอมต้องไม่ลดตาม เพราะคิดจาก PV</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>· มีอัตราชั้นที่ 3 ตั้งไว้ 1% ทั้งที่ผังลึก 2 ชั้น — ตั้งใจวางไว้เป็นกับดัก ชั้นเหนือสุดต้องได้ ฿0 ถ้าได้ ฿70 แปลว่าความลึกที่ตั้งไว้ไม่มีผลจริง</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>บันทึกของผู้ทดสอบ</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="17" t="n"/>
-    </row>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
+    <row r="51">
+      <c r="A51" s="20" t="n"/>
+    </row>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
   </sheetData>
-  <mergeCells count="30">
-    <mergeCell ref="A41:F41"/>
+  <mergeCells count="33">
     <mergeCell ref="B11:D11"/>
-    <mergeCell ref="A16:F16"/>
     <mergeCell ref="B14:D14"/>
+    <mergeCell ref="A46:F46"/>
     <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A27:F27"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A47:F50"/>
     <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A51:F54"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="B9:D9"/>
-    <mergeCell ref="A22:F22"/>
     <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="A20:F20"/>
     <mergeCell ref="B24:D24"/>
-    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="B32:D32"/>
     <mergeCell ref="B26:D26"/>
-    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A48:F48"/>
     <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="A45:F45"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3617,21 +3039,21 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Generation — ข้ามคนที่ยังไม่ถึงขั้นตัดสาย</t>
+          <t>Stairstep — หัวหน้าได้เฉพาะส่วนต่างของขั้น</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>บริษัท: uat-plan-generation · ฐานการคำนวณ: ราคาขาย ฿10,000.00</t>
+          <t>บริษัท: uat-plan-stairstep-breakaway · ฐานการคำนวณ: ราคาขาย ฿10,000.00</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>กติกา: เดินขึ้นจากผู้ขาย นับเป็นรุ่นเฉพาะเมื่อเจอคนที่ถึงขั้นตัดสาย คนที่ยังไม่ถึงขั้นถูกข้ามไปเฉย ๆ ไม่ได้เงินและไม่นับเป็นรุ่น</t>
+          <t>กติกา: หัวหน้าแต่ละคนได้เฉพาะส่วนที่อัตราขั้นของตัวเองสูงกว่าขั้นของลูกทีม และหยุดทันทีที่เจอคนที่ถึงขั้นตัดสาย</t>
         </is>
       </c>
     </row>
@@ -3693,14 +3115,14 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Generation</t>
+          <t>อันดับ (Stairstep)</t>
         </is>
       </c>
       <c r="C9" s="9" t="n"/>
       <c r="D9" s="10" t="n"/>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>ชิปของแผนอื่นต้องกดไม่ได้และมีรูปกุญแจ</t>
+          <t>ชื่อบนชิปเขียนแบบนี้ ไม่ใช่ “Stairstep” เฉย ๆ</t>
         </is>
       </c>
       <c r="F9" s="13" t="inlineStr"/>
@@ -3740,7 +3162,7 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>ขั้นที่ 2 · ฟอร์ม “ค่าตั้งระดับบริษัทของแผน Generation”</t>
+          <t>ขั้นที่ 2 · ฟอร์ม “ค่าตั้งระดับบริษัทของแผนอันดับ (Stairstep)”</t>
         </is>
       </c>
       <c r="B12" s="9" t="n"/>
@@ -3752,92 +3174,104 @@
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>ความลึกสูงสุด (จำนวน Generation)</t>
+          <t>หน้าต่างคำนวณยอดย้อนหลัง (วัน)</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>90</t>
         </is>
       </c>
       <c r="C13" s="9" t="n"/>
       <c r="D13" s="10" t="n"/>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>ฟอร์มนี้มีช่องเดียว — ถ้าเห็นมากกว่านี้ แสดงว่าดูผิดแผน</t>
+          <t>ช่องนี้เคยว่างเพราะคำสั่ง seed ไม่ได้เขียนแถวค่าตั้งให้ — แก้แล้ว 2026-09-22</t>
         </is>
       </c>
       <c r="F13" s="13" t="inlineStr"/>
     </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>ขั้นที่ 2 · รายการ “อัตราค่าแนะนำตาม Generation”</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="n"/>
+    <row r="14" ht="14" customHeight="1">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>ความถี่คำนวณอันดับใหม่</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>รายเดือน</t>
+        </is>
+      </c>
       <c r="C14" s="9" t="n"/>
-      <c r="D14" s="9" t="n"/>
-      <c r="E14" s="9" t="n"/>
-      <c r="F14" s="10" t="n"/>
-    </row>
-    <row r="15" ht="14" customHeight="1">
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>อีกสองตัวเลือกคือ รายวัน / รายสัปดาห์</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr"/>
+    </row>
+    <row r="15" ht="28" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Generation 1</t>
+          <t>นับยอดของใคร</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Generation 1 — 5.00%</t>
+          <t>เฉพาะยอดที่ขายเอง (ค่าเริ่มต้น — เท่าเดิม)</t>
         </is>
       </c>
       <c r="C15" s="9" t="n"/>
       <c r="D15" s="10" t="n"/>
-      <c r="E15" s="12" t="inlineStr"/>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>ตั้งเป็นค่าเริ่มต้นของระบบไว้ · ถ้าเลือก “ยอดทั้งทีม” ต้องมีข้อความเหลืองเตือนขึ้นทันที</t>
+        </is>
+      </c>
       <c r="F15" s="13" t="inlineStr"/>
     </row>
-    <row r="16" ht="14" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>Generation 2</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="inlineStr">
-        <is>
-          <t>Generation 2 — 3.00%</t>
-        </is>
-      </c>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>ขั้นที่ 2 · รายการ “บันไดอันดับ”</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="n"/>
       <c r="C16" s="9" t="n"/>
-      <c r="D16" s="10" t="n"/>
-      <c r="E16" s="12" t="inlineStr">
-        <is>
-          <t>ต้องมีแค่ 2 รายการ ให้เท่ากับความลึกที่ตั้งไว้</t>
-        </is>
-      </c>
-      <c r="F16" s="13" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>ขั้นที่ 3 · สมาชิกผู้ขายได้กี่เปอร์เซ็นต์</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="n"/>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="9" t="n"/>
+      <c r="F16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>อันดับที่ 1</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>1. UAT ขั้นเริ่มต้น · ยอดขั้นต่ำ 0.00 · อัตรา 5.00%</t>
+        </is>
+      </c>
       <c r="C17" s="9" t="n"/>
-      <c r="D17" s="9" t="n"/>
-      <c r="E17" s="9" t="n"/>
-      <c r="F17" s="10" t="n"/>
-    </row>
-    <row r="18" ht="14" customHeight="1">
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>ชื่อขั้นขึ้นต้นด้วย “UAT ” ทุกอัน — ถ้าไม่มีคำนี้ แปลว่าเป็นข้อมูลของบริษัทอื่น</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr"/>
+    </row>
+    <row r="18" ht="28" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>ค่าเริ่มต้นทั้งบริษัท</t>
+          <t>อันดับที่ 2</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>10.00%</t>
+          <t>2. UAT ขั้นผู้นำ · ยอดขั้นต่ำ 50,000.00 · อัตรา 12.00%</t>
         </is>
       </c>
       <c r="C18" s="9" t="n"/>
@@ -3845,166 +3279,166 @@
       <c r="E18" s="12" t="inlineStr"/>
       <c r="F18" s="13" t="inlineStr"/>
     </row>
-    <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>ขั้นที่ 4 · ส่วนเพิ่มเติม</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="n"/>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>อันดับที่ 3</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>3. UAT ขั้นผู้จัดการ (Breakaway) · ยอดขั้นต่ำ 200,000.00 · อัตรา 20.00%</t>
+        </is>
+      </c>
       <c r="C19" s="9" t="n"/>
-      <c r="D19" s="9" t="n"/>
-      <c r="E19" s="9" t="n"/>
-      <c r="F19" s="10" t="n"/>
-    </row>
-    <row r="20" ht="28" customHeight="1">
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>ป้าย “(Breakaway)” สีเหลืองต้องขึ้นเฉพาะอันดับนี้</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr"/>
+    </row>
+    <row r="20" ht="42" customHeight="1">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>4.1 เงินของหัวหน้าทีมมาจากไหน</t>
+          <t>อันดับที่ 4</t>
         </is>
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>บริษัทจ่ายเพิ่ม</t>
+          <t>4. UAT ขั้นผู้อำนวยการ · ยอดขั้นต่ำ 500,000.00 · อัตรา 25.00%</t>
         </is>
       </c>
       <c r="C20" s="9" t="n"/>
       <c r="D20" s="10" t="n"/>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>ป้าย “ตอนนี้: บริษัทจ่ายเพิ่ม” ที่หัวการ์ด · เป็นค่าเริ่มต้นของระบบ คำสั่ง seed ไม่ได้แตะ</t>
+          <t>มีไว้เพื่อให้ “ขั้นตัดสาย” มีอะไรให้หยุด — ขั้นนี้สูงกว่าผู้จัดการ ถ้าการเดินสายไม่หยุดจริง เขาจะได้ ฿500</t>
         </is>
       </c>
       <c r="F20" s="13" t="inlineStr"/>
     </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>4.2 จ่ายขึ้นไปกี่ชั้น</t>
-        </is>
-      </c>
-      <c r="B21" s="12" t="inlineStr">
-        <is>
-          <t>กล่องนี้ต้องไม่ขึ้นเลย</t>
-        </is>
-      </c>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>ขั้นที่ 3 · สมาชิกผู้ขายได้กี่เปอร์เซ็นต์</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="n"/>
       <c r="C21" s="9" t="n"/>
-      <c r="D21" s="10" t="n"/>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>มีเฉพาะบริษัทที่ใช้แผน Unilevel — แผนอื่นจำกัดชั้นด้วยค่าของตัวเอง</t>
-        </is>
-      </c>
-      <c r="F21" s="13" t="inlineStr"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="10" t="n"/>
     </row>
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>4.3 อัตราหัวหน้าทีม · ค่าเริ่มต้นทั้งบริษัท</t>
+          <t>ค่าเริ่มต้นทั้งบริษัท</t>
         </is>
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>ไม่มีรายการ</t>
+          <t>5.00%</t>
         </is>
       </c>
       <c r="C22" s="9" t="n"/>
       <c r="D22" s="10" t="n"/>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>แผนนี้จ่ายชั้นบนด้วยอัตราตามรุ่นข้างบน ไม่ได้ใช้อัตราหัวหน้าทีม</t>
+          <t>ตั้งให้เท่ากับอัตราของ “UAT ขั้นเริ่มต้น” โดยตั้งใจ — อ่านหมายเหตุในขั้นที่ 3 ของชีตนี้</t>
         </is>
       </c>
       <c r="F22" s="13" t="inlineStr"/>
     </row>
-    <row r="23" ht="14" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>4.7 ยอดขั้นต่ำในการเบิก</t>
-        </is>
-      </c>
-      <c r="B23" s="12" t="inlineStr">
-        <is>
-          <t>เว้นว่าง</t>
-        </is>
-      </c>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>ขั้นที่ 4 · ส่วนเพิ่มเติม</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="n"/>
       <c r="C23" s="9" t="n"/>
-      <c r="D23" s="10" t="n"/>
-      <c r="E23" s="12" t="inlineStr">
-        <is>
-          <t>เว้นว่าง = ไม่มีขั้นต่ำ</t>
-        </is>
-      </c>
-      <c r="F23" s="13" t="inlineStr"/>
-    </row>
-    <row r="24" ht="14" customHeight="1">
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="28" customHeight="1">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>4.8 ภาษีหัก ณ ที่จ่าย</t>
+          <t>4.1 เงินของหัวหน้าทีมมาจากไหน</t>
         </is>
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>ไม่หัก (เว้นว่าง)</t>
+          <t>บริษัทจ่ายเพิ่ม</t>
         </is>
       </c>
       <c r="C24" s="9" t="n"/>
       <c r="D24" s="10" t="n"/>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>มีบริษัทเดียวในชุดนี้ที่หัก คือ Affiliate</t>
+          <t>ป้าย “ตอนนี้: บริษัทจ่ายเพิ่ม” ที่หัวการ์ด · เป็นค่าเริ่มต้นของระบบ คำสั่ง seed ไม่ได้แตะ</t>
         </is>
       </c>
       <c r="F24" s="13" t="inlineStr"/>
     </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>ไม่ได้อยู่บนหน้านี้ — ตรวจที่อื่น</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="n"/>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>4.2 จ่ายขึ้นไปกี่ชั้น</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>กล่องนี้ต้องไม่ขึ้นเลย</t>
+        </is>
+      </c>
       <c r="C25" s="9" t="n"/>
-      <c r="D25" s="9" t="n"/>
-      <c r="E25" s="9" t="n"/>
-      <c r="F25" s="10" t="n"/>
-    </row>
-    <row r="26" ht="56" customHeight="1">
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>มีเฉพาะบริษัทที่ใช้แผน Unilevel — แผนอื่นจำกัดชั้นด้วยค่าของตัวเอง</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr"/>
+    </row>
+    <row r="26" ht="28" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>บันไดอันดับ (ใช้ตัดสินว่าใคร “ตัดสาย”)</t>
+          <t>4.3 อัตราหัวหน้าทีม · ค่าเริ่มต้นทั้งบริษัท</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>UAT ขั้นเริ่มต้น 5% · UAT ขั้นผู้นำ 10% · UAT ขั้นผู้จัดการ 15% (Breakaway)</t>
+          <t>ไม่มีรายการ</t>
         </is>
       </c>
       <c r="C26" s="9" t="n"/>
       <c r="D26" s="10" t="n"/>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>หน้าตั้งค่าของบริษัทที่ใช้แผน Generation ไม่แสดงฟอร์มบันไดอันดับเลย ทั้งที่แผนนี้ใช้มันคำนวณ — ข้อมูลถูกสร้างไว้ให้แล้ว แต่ตรวจบนหน้าจอนี้ไม่ได้ ถือเป็นข้อสังเกตที่ควรรายงาน</t>
+          <t>แผนนี้จ่ายชั้นบนด้วยส่วนต่างของอันดับ ไม่ได้ใช้อัตราหัวหน้าทีม</t>
         </is>
       </c>
       <c r="F26" s="13" t="inlineStr"/>
     </row>
-    <row r="27" ht="28" customHeight="1">
+    <row r="27" ht="14" customHeight="1">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>อันดับปัจจุบันของแต่ละคน</t>
+          <t>4.7 ยอดขั้นต่ำในการเบิก</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>ข และ ง = ขั้นผู้จัดการ (ตัดสาย) · ก, ค, ผู้ขาย = ขั้นเริ่มต้น</t>
+          <t>เว้นว่าง</t>
         </is>
       </c>
       <c r="C27" s="9" t="n"/>
       <c r="D27" s="10" t="n"/>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>นี่คือสิ่งที่ทำให้ ก และ ค ถูกข้าม — ดูขั้นที่ 2 ของชีตนี้</t>
+          <t>เว้นว่าง = ไม่มีขั้นต่ำ</t>
         </is>
       </c>
       <c r="F27" s="13" t="inlineStr"/>
@@ -4012,162 +3446,136 @@
     <row r="28" ht="14" customHeight="1">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>สายงาน (ใครเป็นหัวหน้าของใคร)</t>
+          <t>4.8 ภาษีหัก ณ ที่จ่าย</t>
         </is>
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>ผู้ขาย → ก → ข (ตัดสาย) → ค → ง (ตัดสาย)</t>
+          <t>ไม่หัก (เว้นว่าง)</t>
         </is>
       </c>
       <c r="C28" s="9" t="n"/>
       <c r="D28" s="10" t="n"/>
       <c r="E28" s="12" t="inlineStr">
         <is>
+          <t>มีบริษัทเดียวในชุดนี้ที่หัก คือ Affiliate</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>ไม่ได้อยู่บนหน้านี้ — ตรวจที่อื่น</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>อันดับปัจจุบันของแต่ละคน</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>ผู้ขาย = เริ่มต้น · ผู้นำ = ผู้นำ · ผู้จัดการ = ผู้จัดการ (ตัดสาย) · ผู้อำนวยการ = ผู้อำนวยการ</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>คำสั่ง seed วางอันดับให้โดยตรง ไม่ได้รอรอบคำนวณ — หน้าค่าแนะนำไม่มีช่องให้ดูหรือแก้อันดับรายคน</t>
+        </is>
+      </c>
+      <c r="F30" s="13" t="inlineStr"/>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>สายงาน (ใครเป็นหัวหน้าของใคร)</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>ผู้ขาย → ผู้นำ → ผู้จัดการ (ตัดสาย) → ผู้อำนวยการ</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
           <t>ดูที่เมนูจัดการผู้ใช้ระบบ ช่อง “หัวหน้า”</t>
         </is>
       </c>
-      <c r="F28" s="13" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="F31" s="13" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>ขั้นที่ 2 — ตรวจว่าค่าคอมที่ลงบัญชีตรงกับนี้</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>ใคร</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>ได้จาก (earned_via)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>อัตรา</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>ควรได้ (บาท)</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="E34" s="6" t="inlineStr">
         <is>
           <t>ที่มาของตัวเลข</t>
         </is>
       </c>
-      <c r="F31" s="6" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <t>ผ่าน / ไม่ผ่าน</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="12" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t>UAT ผู้ขาย</t>
         </is>
       </c>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>direct</t>
         </is>
       </c>
-      <c r="C32" s="12" t="inlineStr">
-        <is>
-          <t>10.00%</t>
-        </is>
-      </c>
-      <c r="D32" s="14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E32" s="12" t="inlineStr">
-        <is>
-          <t>10% ของ ฿10,000</t>
-        </is>
-      </c>
-      <c r="F32" s="13" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="18" t="inlineStr">
-        <is>
-          <t>UAT หัวหน้า ก</t>
-        </is>
-      </c>
-      <c r="B33" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C33" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D33" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="19" t="inlineStr">
-        <is>
-          <t>ยังไม่ถึงขั้นตัดสาย → ถูกข้าม ไม่มีแถวในบัญชี</t>
-        </is>
-      </c>
-      <c r="F33" s="13" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="12" t="inlineStr">
-        <is>
-          <t>UAT หัวหน้า ข (ตัดสาย)</t>
-        </is>
-      </c>
-      <c r="B34" s="12" t="inlineStr">
-        <is>
-          <t>generation_override</t>
-        </is>
-      </c>
-      <c r="C34" s="12" t="inlineStr">
+      <c r="C35" s="12" t="inlineStr">
         <is>
           <t>5.00%</t>
         </is>
       </c>
-      <c r="D34" s="14" t="n">
+      <c r="D35" s="14" t="n">
         <v>500</v>
       </c>
-      <c r="E34" s="12" t="inlineStr">
-        <is>
-          <t>รุ่นที่ 1</t>
-        </is>
-      </c>
-      <c r="F34" s="13" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="18" t="inlineStr">
-        <is>
-          <t>UAT หัวหน้า ค</t>
-        </is>
-      </c>
-      <c r="B35" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C35" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D35" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="19" t="inlineStr">
-        <is>
-          <t>ยังไม่ถึงขั้นตัดสาย → ถูกข้าม ไม่มีแถวในบัญชี</t>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>5% ของ ฿10,000</t>
         </is>
       </c>
       <c r="F35" s="13" t="inlineStr"/>
@@ -4175,129 +3583,200 @@
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>UAT หัวหน้า ง (ตัดสาย)</t>
+          <t>UAT ผู้นำ</t>
         </is>
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>generation_override</t>
+          <t>stairstep_override</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>7.00%</t>
         </is>
       </c>
       <c r="D36" s="14" t="n">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>รุ่นที่ 2</t>
+          <t>ส่วนต่าง 12% − 5% = 7%</t>
         </is>
       </c>
       <c r="F36" s="13" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="C37" s="15" t="inlineStr">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>UAT ผู้จัดการ (ตัดสาย)</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>stairstep_override</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>8.00%</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="n">
+        <v>800</v>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>ส่วนต่าง 20% − 12% = 8%</t>
+        </is>
+      </c>
+      <c r="F37" s="13" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>UAT ผู้อำนวยการ</t>
+        </is>
+      </c>
+      <c r="B38" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D38" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="16" t="inlineStr">
+        <is>
+          <t>ขั้นสูงกว่าผู้จัดการ (25%) แต่ใต้เขาเป็นขั้นตัดสาย → การเดินสายหยุดตรงนั้น ต้องไม่มีแถว ถ้าได้ ฿500 แปลว่าระบบไม่สนขั้นตัดสาย</t>
+        </is>
+      </c>
+      <c r="F38" s="13" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="C39" s="18" t="inlineStr">
         <is>
           <t>รวมจ่ายออก</t>
         </is>
       </c>
-      <c r="D37" s="16">
-        <f>SUM(D32:D36)</f>
+      <c r="D39" s="19">
+        <f>SUM(D35:D38)</f>
         <v/>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>ขั้นที่ 3 — จุดที่มักพลาด</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>· หัวหน้า ก อยู่เหนือผู้ขายโดยตรงแต่ได้ ฿0 — นี่คือพฤติกรรมที่ถูกต้องของแผนนี้ และเป็นเรื่องที่คนใช้งานจริงจะร้องเรียนมากที่สุด</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>· ต้องมีแค่ 3 แถวในบัญชี ไม่ใช่ 5 — คนที่ถูกข้ามต้องไม่มีแถว ฿0</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1">
+    <row r="42" ht="30" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>· ลองเลื่อน ก ขึ้นเป็นขั้นตัดสาย: ก ต้องกลายเป็นรุ่นที่ 1 และ ง ต้องหลุดออกไป (เพราะจำกัด 2 รุ่น)</t>
+          <t>· สามแถวได้ไม่เท่ากันโดยตั้งใจ (500 / 700 / 800) — ถ้าเท่ากันหมด การสลับแถวจะมองไม่เห็น ชุดนี้เคยเป็น 500 ทั้งสามแถว แล้วพิสูจน์อะไรไม่ได้เลย</t>
         </is>
       </c>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>· หน้าตั้งค่าของแผนนี้ไม่แสดงบันไดอันดับเลย ทั้งที่ “ตัดสาย” คือหัวใจของการคำนวณ — ข้อมูลอันดับถูกสร้างไว้ให้แล้ว แต่ตรวจจากหน้าจอนี้ไม่ได้ ถือเป็นข้อสังเกตที่ควรรายงาน</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+          <t>· ผู้อำนวยการอยู่เหนือผู้จัดการและมีขั้นสูงกว่า (25%) แต่ต้องได้ ฿0 เพราะใต้เขาเป็นขั้นตัดสาย — ถ้าได้ ฿500 แปลว่าระบบไม่ได้หยุดที่ขั้นตัดสายจริง</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>· คำถามออกแบบที่ยังค้าง: อัตราของผู้ขายมาจาก commission_rules ไม่ได้มาจากขั้นของตัวเอง ชุดทดสอบนี้จงใจตั้งให้ตรงกันไว้ ถ้าตั้งไม่ตรงกันจะมี 'อัตราผู้ขาย' สองค่าบนหน้าจอเดียว</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>· ลองเลื่อนผู้ขายขึ้นเป็นขั้นตัดสาย: หัวหน้าทุกคนเหนือขึ้นไปต้องได้ ฿0 ทันที</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>· ฟอร์มสามช่องบนสุด (หน้าต่างย้อนหลัง / ความถี่ / นับยอดของใคร) เคยว่างเปล่าจนถึง 2026-09-22 เพราะคำสั่ง seed ไม่ได้เขียนแถวค่าตั้งให้ — ถ้ายังว่างอยู่ แปลว่ารันคำสั่ง seed เวอร์ชันเก่า</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>· ค่าในสามช่องนั้นใช้โดยรอบคำนวณอันดับอัตโนมัติ ซึ่งชุดทดสอบนี้ไม่ได้รัน (อันดับของทุกคนถูกวางไว้โดยตรง) — จึงเปลี่ยนค่าแล้วยอดในขั้นที่ 2 ต้องไม่ขยับ</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>บันทึกของผู้ทดสอบ</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="17" t="n"/>
-    </row>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
+    <row r="50">
+      <c r="A50" s="20" t="n"/>
+    </row>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
   </sheetData>
-  <mergeCells count="27">
-    <mergeCell ref="A41:F41"/>
+  <mergeCells count="32">
     <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="B17:D17"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A21:F21"/>
     <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A42:F42"/>
-    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A23:F23"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="B9:D9"/>
-    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="B30:D30"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A29:F29"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="A43:F43"/>
     <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A44:F44"/>
     <mergeCell ref="B26:D26"/>
-    <mergeCell ref="A40:F40"/>
     <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="A50:F53"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="B22:D22"/>
+    <mergeCell ref="A45:F45"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="A46:F49"/>
-    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4311,21 +3790,21 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>พันธมิตร (Affiliate) — จ่ายขึ้นไปชั้นเดียว</t>
+          <t>Generation — ข้ามคนที่ยังไม่ถึงขั้นตัดสาย</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>บริษัท: uat-plan-affiliate · ฐานการคำนวณ: ราคาขาย ฿10,000.00</t>
+          <t>บริษัท: uat-plan-generation · ฐานการคำนวณ: ราคาขาย ฿10,000.00</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>กติกา: ผู้แนะนำโดยตรงได้ส่วนแบ่งชั้นเดียว ไม่เดินขึ้นต่อ</t>
+          <t>กติกา: เดินขึ้นจากผู้ขาย นับเป็นรุ่นเฉพาะเมื่อเจอคนที่ถึงขั้นตัดสาย คนที่ยังไม่ถึงขั้นถูกข้ามไปเฉย ๆ ไม่ได้เงินและไม่นับเป็นรุ่น</t>
         </is>
       </c>
     </row>
@@ -4387,14 +3866,14 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>พันธมิตร (Affiliate)</t>
+          <t>Generation</t>
         </is>
       </c>
       <c r="C9" s="9" t="n"/>
       <c r="D9" s="10" t="n"/>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>ชื่อบนชิปเขียนแบบนี้ ไม่ใช่ “Affiliate” เฉย ๆ</t>
+          <t>ชิปของแผนอื่นต้องกดไม่ได้และมีรูปกุญแจ</t>
         </is>
       </c>
       <c r="F9" s="13" t="inlineStr"/>
@@ -4434,7 +3913,7 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>ขั้นที่ 2 · ฟอร์ม “ค่าตั้งระดับบริษัทของแผนพันธมิตร (Affiliate)”</t>
+          <t>ขั้นที่ 2 · ฟอร์ม “ค่าตั้งระดับบริษัทของแผน Generation”</t>
         </is>
       </c>
       <c r="B12" s="9" t="n"/>
@@ -4446,6 +3925,751 @@
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
         <is>
+          <t>ความลึกสูงสุด (จำนวน Generation)</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>ฟอร์มนี้มีช่องเดียว · ตั้งใจให้น้อยกว่าจำนวนอัตราข้างล่าง เพื่อให้ตรวจได้ว่าค่านี้บังคับจริง</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>ขั้นที่ 2 · รายการ “อัตราค่าแนะนำตาม Generation”</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="10" t="n"/>
+    </row>
+    <row r="15" ht="14" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Generation 1</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Generation 1 — 5.00%</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="12" t="inlineStr"/>
+      <c r="F15" s="13" t="inlineStr"/>
+    </row>
+    <row r="16" ht="14" customHeight="1">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Generation 2</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Generation 2 — 3.00%</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="12" t="inlineStr"/>
+      <c r="F16" s="13" t="inlineStr"/>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>Generation 3</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Generation 3 — 1.00%</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>ตั้งไว้แต่ไม่มีวันได้จ่าย เพราะจำกัดไว้ 2 รุ่น — ตัวล่อแบบเดียวกับ Level 3 ของ Matrix</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>ขั้นที่ 3 · สมาชิกผู้ขายได้กี่เปอร์เซ็นต์</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="9" t="n"/>
+      <c r="F18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="14" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>ค่าเริ่มต้นทั้งบริษัท</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>10.00%</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="12" t="inlineStr"/>
+      <c r="F19" s="13" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>ขั้นที่ 4 · ส่วนเพิ่มเติม</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="10" t="n"/>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>4.1 เงินของหัวหน้าทีมมาจากไหน</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>บริษัทจ่ายเพิ่ม</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>ป้าย “ตอนนี้: บริษัทจ่ายเพิ่ม” ที่หัวการ์ด · เป็นค่าเริ่มต้นของระบบ คำสั่ง seed ไม่ได้แตะ</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr"/>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>4.2 จ่ายขึ้นไปกี่ชั้น</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>กล่องนี้ต้องไม่ขึ้นเลย</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>มีเฉพาะบริษัทที่ใช้แผน Unilevel — แผนอื่นจำกัดชั้นด้วยค่าของตัวเอง</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr"/>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>4.3 อัตราหัวหน้าทีม · ค่าเริ่มต้นทั้งบริษัท</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>ไม่มีรายการ</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>แผนนี้จ่ายชั้นบนด้วยอัตราตามรุ่นข้างบน ไม่ได้ใช้อัตราหัวหน้าทีม</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr"/>
+    </row>
+    <row r="24" ht="14" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>4.7 ยอดขั้นต่ำในการเบิก</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>เว้นว่าง</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="10" t="n"/>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>เว้นว่าง = ไม่มีขั้นต่ำ</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="inlineStr"/>
+    </row>
+    <row r="25" ht="14" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>4.8 ภาษีหัก ณ ที่จ่าย</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>ไม่หัก (เว้นว่าง)</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="n"/>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>มีบริษัทเดียวในชุดนี้ที่หัก คือ Affiliate</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>ไม่ได้อยู่บนหน้านี้ — ตรวจที่อื่น</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="10" t="n"/>
+    </row>
+    <row r="27" ht="56" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>บันไดอันดับ (ใช้ตัดสินว่าใคร “ตัดสาย”)</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>UAT ขั้นเริ่มต้น 5% · UAT ขั้นผู้จัดการ 20% (Breakaway) — สร้างไว้ 2 ขั้นพอ เพราะแผนนี้ใช้แค่ว่า “ตัดสายหรือยัง”</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="n"/>
+      <c r="D27" s="10" t="n"/>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>หน้าตั้งค่าของบริษัทที่ใช้แผน Generation ไม่แสดงฟอร์มบันไดอันดับเลย ทั้งที่แผนนี้ใช้มันคำนวณ — ข้อมูลถูกสร้างไว้ให้แล้ว แต่ตรวจบนหน้าจอนี้ไม่ได้ ถือเป็นข้อสังเกตที่ควรรายงาน</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="inlineStr"/>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>อันดับปัจจุบันของแต่ละคน</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>ข, ง และ จ = ขั้นผู้จัดการ (ตัดสาย) · ก, ค, ผู้ขาย = ขั้นเริ่มต้น</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>นี่คือสิ่งที่ทำให้ ก และ ค ถูกข้าม — ดูขั้นที่ 2 ของชีตนี้</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="inlineStr"/>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>สายงาน (ใครเป็นหัวหน้าของใคร)</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>ผู้ขาย → ก → ข (ตัดสาย) → ค → ง (ตัดสาย) → จ (ตัดสาย)</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>ดูที่เมนูจัดการผู้ใช้ระบบ ช่อง “หัวหน้า”</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>ขั้นที่ 2 — ตรวจว่าค่าคอมที่ลงบัญชีตรงกับนี้</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>ใคร</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>ได้จาก (earned_via)</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>อัตรา</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>ควรได้ (บาท)</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>ที่มาของตัวเลข</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>ผ่าน / ไม่ผ่าน</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>UAT ผู้ขาย</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>10.00%</t>
+        </is>
+      </c>
+      <c r="D33" s="14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>10% ของ ฿10,000</t>
+        </is>
+      </c>
+      <c r="F33" s="13" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>UAT หัวหน้า ก</t>
+        </is>
+      </c>
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D34" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="16" t="inlineStr">
+        <is>
+          <t>ยังไม่ถึงขั้นตัดสาย → ถูกข้าม ไม่มีแถวในบัญชี</t>
+        </is>
+      </c>
+      <c r="F34" s="13" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>UAT หัวหน้า ข (ตัดสาย)</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>generation_override</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="n">
+        <v>500</v>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>รุ่นที่ 1</t>
+        </is>
+      </c>
+      <c r="F35" s="13" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="15" t="inlineStr">
+        <is>
+          <t>UAT หัวหน้า ค</t>
+        </is>
+      </c>
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D36" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="16" t="inlineStr">
+        <is>
+          <t>ยังไม่ถึงขั้นตัดสาย → ถูกข้าม ไม่มีแถวในบัญชี</t>
+        </is>
+      </c>
+      <c r="F36" s="13" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>UAT หัวหน้า ง (ตัดสาย)</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>generation_override</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>3.00%</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="n">
+        <v>300</v>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>รุ่นที่ 2</t>
+        </is>
+      </c>
+      <c r="F37" s="13" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>UAT หัวหน้า จ (ตัดสาย)</t>
+        </is>
+      </c>
+      <c r="B38" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D38" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="16" t="inlineStr">
+        <is>
+          <t>ตัดสายเหมือน ข และ ง ทุกอย่าง ต่างกันแค่เป็นรุ่นที่ 3 · ตั้งอัตรารุ่นที่ 3 ไว้ 1% แต่จำกัดไว้ 2 รุ่น → ต้องไม่มีแถว ถ้าได้ ฿100 แปลว่าระบบไม่สนจำนวนรุ่นสูงสุด</t>
+        </is>
+      </c>
+      <c r="F38" s="13" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="C39" s="18" t="inlineStr">
+        <is>
+          <t>รวมจ่ายออก</t>
+        </is>
+      </c>
+      <c r="D39" s="19">
+        <f>SUM(D33:D38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>ขั้นที่ 3 — จุดที่มักพลาด</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>· หัวหน้า ก อยู่เหนือผู้ขายโดยตรงแต่ได้ ฿0 — นี่คือพฤติกรรมที่ถูกต้องของแผนนี้ และเป็นเรื่องที่คนใช้งานจริงจะร้องเรียนมากที่สุด</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>· ต้องมีแค่ 3 แถวในบัญชี ไม่ใช่ 5 — คนที่ถูกข้ามต้องไม่มีแถว ฿0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>· ลองเลื่อน ก ขึ้นเป็นขั้นตัดสาย: ก ต้องกลายเป็นรุ่นที่ 1 และ ง ต้องหลุดออกไป (เพราะจำกัด 2 รุ่น)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>· จ ตัดสายแล้วเหมือน ข และ ง ทุกอย่าง ต่างกันแค่เป็นรุ่นที่ 3 และมีอัตรารุ่นที่ 3 ตั้งไว้ 1% — ต้องได้ ฿0 ถ้าได้ ฿100 แปลว่าจำนวนรุ่นสูงสุดไม่มีผลจริง</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>· หน้าตั้งค่าของแผนนี้ไม่แสดงบันไดอันดับเลย ทั้งที่ “ตัดสาย” คือหัวใจของการคำนวณ — ข้อมูลอันดับถูกสร้างไว้ให้แล้ว แต่ตรวจจากหน้าจอนี้ไม่ได้ ถือเป็นข้อสังเกตที่ควรรายงาน</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>บันทึกของผู้ทดสอบ</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="20" t="n"/>
+    </row>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+  </sheetData>
+  <mergeCells count="29">
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A49:F52"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B21:D21"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>พันธมิตร (Affiliate) — จ่ายขึ้นไปชั้นเดียว</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>บริษัท: uat-plan-affiliate · ฐานการคำนวณ: ราคาขาย ฿10,000.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>กติกา: ผู้แนะนำโดยตรงได้ส่วนแบ่งชั้นเดียว ไม่เดินขึ้นต่อ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>ขั้นที่ 1 — เปิดหน้า “ค่าแนะนำ” ของบริษัทนี้ แล้วไล่ตรวจทีละช่อง</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>แถบสีคือหัวข้อของส่วนบนหน้าจอ · ชื่อในคอลัมน์ “ช่องบนหน้าจอ” เขียนตรงตามที่หน้าจอเขียนไว้</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>ช่องบนหน้าจอ</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>ต้องเป็น</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>หมายเหตุ</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>ตรงไหม</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>ขั้นที่ 2 · แถวชิปเลือกแผน</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="10" t="n"/>
+    </row>
+    <row r="9" ht="14" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>แผนที่เลือกอยู่</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>พันธมิตร (Affiliate)</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>ชื่อบนชิปเขียนแบบนี้ ไม่ใช่ “Affiliate” เฉย ๆ</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>ขั้นที่ 2 · การ์ด “ค่าแนะนำคิดจากอะไร”</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="14" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>ฐานการคำนวณ</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>ราคาขาย</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>ทั้งสองปุ่มกดไม่ได้</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>ขั้นที่ 2 · ฟอร์ม “ค่าตั้งระดับบริษัทของแผนพันธมิตร (Affiliate)”</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="9" t="n"/>
+      <c r="E12" s="9" t="n"/>
+      <c r="F12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
           <t>หน้าต่างนับเครดิต (วัน)</t>
         </is>
       </c>
@@ -4647,7 +4871,7 @@
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>ผู้ขาย → ผู้แนะนำ</t>
+          <t>ผู้ขาย → ผู้แนะนำ → ผู้แนะนำชั้นบน</t>
         </is>
       </c>
       <c r="C24" s="9" t="n"/>
@@ -4751,74 +4975,100 @@
       <c r="F29" s="13" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="C30" s="15" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>UAT ผู้แนะนำชั้นบน</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="16" t="inlineStr">
+        <is>
+          <t>ผ่าน Basic แล้วและอัตราเดียวกันใช้กับเขาได้ แต่แผนนี้จ่ายขึ้นชั้นเดียว → ต้องไม่มีแถว ถ้าได้ ฿300 แปลว่าระบบเดินสายแบบ Unilevel</t>
+        </is>
+      </c>
+      <c r="F30" s="13" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="C31" s="18" t="inlineStr">
         <is>
           <t>รวมจ่ายออก</t>
         </is>
       </c>
-      <c r="D30" s="16">
-        <f>SUM(D28:D29)</f>
+      <c r="D31" s="19">
+        <f>SUM(D28:D30)</f>
         <v/>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>ขั้นที่ 3 — จุดที่มักพลาด</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>· จบแค่ชั้นเดียว — ถ้าผู้แนะนำมีหัวหน้าอีกชั้น คนนั้นต้องไม่ได้อะไร</t>
         </is>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>· จบแค่ชั้นเดียว — ผู้แนะนำชั้นบนมีตัวตนจริง ผ่าน Basic แล้ว และอัตราเดียวกันใช้กับเขาได้ แต่ต้องได้ ฿0 · นี่คือสิ่งเดียวที่แยกแผนนี้ออกจาก Unilevel บนชุดทดสอบนี้</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
           <t>· อัตรา 3% ของผู้แนะนำอยู่ที่ขั้นที่ 4 ข้อ 4.3 ไม่ได้อยู่ในฟอร์มของแผนในขั้นที่ 2 — ฟอร์มในขั้นที่ 2 คุมแค่หน้าต่างนับเครดิตของลิงก์พันธมิตร</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>· ลองสลับเป็นโหมด deductive: ผู้ขายต้องเหลือ ฿700 และยอดจ่ายออกรวมต้องเท่าเดิมที่ ฿1,000</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>· ลองสลับเป็นโหมด deductive: ผู้ขายต้องเหลือ ฿700 และยอดจ่ายออกรวมต้องเท่าเดิมที่ ฿1,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
           <t>· บริษัทนี้หักภาษี ณ ที่จ่าย 3% — ยอดในตารางนี้คือยอดก่อนหัก ดูยอดโอนจริงในชีต 8</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>บันทึกของผู้ทดสอบ</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="17" t="n"/>
-    </row>
-    <row r="40"/>
+    <row r="40">
+      <c r="A40" s="20" t="n"/>
+    </row>
     <row r="41"/>
     <row r="42"/>
+    <row r="43"/>
   </sheetData>
   <mergeCells count="23">
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="B14:D14"/>
+    <mergeCell ref="A37:F37"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A39:F42"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A40:F43"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="A17:F17"/>
@@ -4891,15 +5141,15 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="n">
+      <c r="A5" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>แถบเทามีไอคอนกุญแจ บอกจำนวนออเดอร์และจำนวนรายการค่าแนะนำ พร้อมวันที่รายการแรก</t>
         </is>
       </c>
-      <c r="C5" s="19" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>ขั้นที่ 2 ใต้ชิปแผน</t>
         </is>
@@ -4923,15 +5173,15 @@
       <c r="D6" s="13" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="n">
+      <c r="A7" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>ชิปของแผนอื่นกดไม่ได้ และมีไอคอนกุญแจบนชิป</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>ขั้นที่ 2 แถวชิป</t>
         </is>
@@ -4955,15 +5205,15 @@
       <c r="D8" s="13" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="n">
+      <c r="A9" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>ปุ่มเลือกฐานการคำนวณ (ราคาขาย / PV) กดไม่ได้</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>ขั้นที่ 2 การ์ด 'ค่าแนะนำคิดจากอะไร'</t>
         </is>
@@ -4987,15 +5237,15 @@
       <c r="D10" s="13" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="n">
+      <c r="A11" s="16" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>กดกล่องในผังแล้วเลื่อนไปที่ช่องตั้งค่านั้น พร้อมกรอบเรืองขึ้นชั่วครู่</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>ขั้นที่ 2 ผังของแผน</t>
         </is>
@@ -5019,15 +5269,15 @@
       <c r="D12" s="13" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="n">
+      <c r="A13" s="16" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>Tab เข้ากล่องในผังได้ และกด Enter / Space แล้วทำงานเหมือนคลิก</t>
         </is>
       </c>
-      <c r="C13" s="19" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>ขั้นที่ 2 ผังของแผน (แป้นพิมพ์)</t>
         </is>
@@ -5116,15 +5366,15 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="n">
+      <c r="A5" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>แถบเหลือง 'มีค่าแนะนำ แต่ตั้งจ่ายไม่ได้' ต้องหายไป และทั้ง 4 คนย้ายมาอยู่ขั้นที่ 1</t>
         </is>
       </c>
-      <c r="C5" s="19" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>UAT · Unilevel → จ่ายค่าแนะนำ</t>
         </is>
@@ -5148,15 +5398,15 @@
       <c r="D6" s="13" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="n">
+      <c r="A7" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>ติ๊กทั้ง 4 คนแล้วตั้งจ่าย → ต้องย้ายไปขั้นที่ 2 'รอคุณตรวจสอบ' ครบ</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>หน้าเดียวกัน</t>
         </is>
@@ -5180,15 +5430,15 @@
       <c r="D8" s="13" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="n">
+      <c r="A9" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>บันทึกการโอน → ย้ายไป 'โอนแล้ว' และแถวในบัญชีเปลี่ยนเป็นจ่ายแล้ว</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>ขั้นที่ 3</t>
         </is>
@@ -5212,15 +5462,15 @@
       <c r="D10" s="13" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="n">
+      <c r="A11" s="16" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>บริษัท Affiliate หักภาษี ณ ที่จ่าย 3% — ยอดที่ได้ ฿1,000 ต้องโอนจริง ฿970 และหน้าจอต้องบอกทั้งสองยอด</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>UAT · Affiliate → จ่ายค่าแนะนำ</t>
         </is>
@@ -5244,15 +5494,15 @@
       <c r="D12" s="13" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="n">
+      <c r="A13" s="16" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>ลองลบบัญชีธนาคารของตัวแทนหนึ่งคนออก → เขาต้องหลุดจากขั้นที่ 1 กลับไปอยู่แถบเหลืองทันที</t>
         </is>
       </c>
-      <c r="C13" s="19" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>จัดการผู้ใช้ระบบ → กลับมาหน้าจ่าย</t>
         </is>
